--- a/data/nzd0260/nzd0260.xlsx
+++ b/data/nzd0260/nzd0260.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y337"/>
+  <dimension ref="A1:Y338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27611,7 +27611,7 @@
         <v>238.2</v>
       </c>
       <c r="K337" t="n">
-        <v>245.69</v>
+        <v>251.46</v>
       </c>
       <c r="L337" t="n">
         <v>269.72</v>
@@ -27655,6 +27655,87 @@
       <c r="Y337" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:42+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>323.17</v>
+      </c>
+      <c r="C338" t="n">
+        <v>300.28</v>
+      </c>
+      <c r="D338" t="n">
+        <v>270.9</v>
+      </c>
+      <c r="E338" t="n">
+        <v>288.07</v>
+      </c>
+      <c r="F338" t="n">
+        <v>299.81</v>
+      </c>
+      <c r="G338" t="n">
+        <v>326.81</v>
+      </c>
+      <c r="H338" t="n">
+        <v>318.4</v>
+      </c>
+      <c r="I338" t="n">
+        <v>311.68</v>
+      </c>
+      <c r="J338" t="n">
+        <v>254.21</v>
+      </c>
+      <c r="K338" t="n">
+        <v>267.8</v>
+      </c>
+      <c r="L338" t="n">
+        <v>281.14</v>
+      </c>
+      <c r="M338" t="n">
+        <v>299.1</v>
+      </c>
+      <c r="N338" t="n">
+        <v>302.57</v>
+      </c>
+      <c r="O338" t="n">
+        <v>314.35</v>
+      </c>
+      <c r="P338" t="n">
+        <v>353.3</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>352.04</v>
+      </c>
+      <c r="R338" t="n">
+        <v>345.81</v>
+      </c>
+      <c r="S338" t="n">
+        <v>343.45</v>
+      </c>
+      <c r="T338" t="n">
+        <v>346.7</v>
+      </c>
+      <c r="U338" t="n">
+        <v>346.74</v>
+      </c>
+      <c r="V338" t="n">
+        <v>348.62</v>
+      </c>
+      <c r="W338" t="n">
+        <v>353.31</v>
+      </c>
+      <c r="X338" t="n">
+        <v>354.86</v>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -27669,7 +27750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B345"/>
+  <dimension ref="A1:B346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31122,6 +31203,16 @@
       </c>
       <c r="B345" t="n">
         <v>-0.57</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -31290,28 +31381,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4138462135225875</v>
+        <v>-0.4104375380247761</v>
       </c>
       <c r="J2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L2" t="n">
-        <v>0.225386875926215</v>
+        <v>0.2228902978266104</v>
       </c>
       <c r="M2" t="n">
-        <v>4.324457972999092</v>
+        <v>4.330271641096472</v>
       </c>
       <c r="N2" t="n">
-        <v>31.63598522915006</v>
+        <v>31.65166878926673</v>
       </c>
       <c r="O2" t="n">
-        <v>5.624587560803908</v>
+        <v>5.625981584511874</v>
       </c>
       <c r="P2" t="n">
-        <v>327.8152392545512</v>
+        <v>327.7793637157498</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31368,28 +31459,28 @@
         <v>0.1297</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4989669426879375</v>
+        <v>-0.4926459785026271</v>
       </c>
       <c r="J3" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K3" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1841669896340322</v>
+        <v>0.1802607806493297</v>
       </c>
       <c r="M3" t="n">
-        <v>5.95478124031303</v>
+        <v>5.972442369328969</v>
       </c>
       <c r="N3" t="n">
-        <v>59.27617855293404</v>
+        <v>59.47790301828248</v>
       </c>
       <c r="O3" t="n">
-        <v>7.699102451125978</v>
+        <v>7.712191842678868</v>
       </c>
       <c r="P3" t="n">
-        <v>301.9157854024227</v>
+        <v>301.849258683749</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31446,28 +31537,28 @@
         <v>0.1644</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1803384989538025</v>
+        <v>-0.1823022946882676</v>
       </c>
       <c r="J4" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K4" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01487602950679945</v>
+        <v>0.01527733616225635</v>
       </c>
       <c r="M4" t="n">
-        <v>8.420515858298973</v>
+        <v>8.40637916357506</v>
       </c>
       <c r="N4" t="n">
-        <v>114.8900458587088</v>
+        <v>114.5822683097304</v>
       </c>
       <c r="O4" t="n">
-        <v>10.71867743048128</v>
+        <v>10.70431073492032</v>
       </c>
       <c r="P4" t="n">
-        <v>279.0720727007808</v>
+        <v>279.092858782794</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31524,28 +31615,28 @@
         <v>0.1682</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.177687335440805</v>
+        <v>-0.1772280049570063</v>
       </c>
       <c r="J5" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K5" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01485431368022416</v>
+        <v>0.01486159407589593</v>
       </c>
       <c r="M5" t="n">
-        <v>7.806992506400718</v>
+        <v>7.785920562102478</v>
       </c>
       <c r="N5" t="n">
-        <v>111.4077609416724</v>
+        <v>111.0761766417885</v>
       </c>
       <c r="O5" t="n">
-        <v>10.55498749130819</v>
+        <v>10.53926831624418</v>
       </c>
       <c r="P5" t="n">
-        <v>291.8655150784806</v>
+        <v>291.86064593681</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31602,28 +31693,28 @@
         <v>0.1057</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2520192461459327</v>
+        <v>-0.2578526751135644</v>
       </c>
       <c r="J6" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K6" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01677076961651236</v>
+        <v>0.0176122789855836</v>
       </c>
       <c r="M6" t="n">
-        <v>11.74965237759526</v>
+        <v>11.7433354674545</v>
       </c>
       <c r="N6" t="n">
-        <v>199.6540518862716</v>
+        <v>199.3746708237939</v>
       </c>
       <c r="O6" t="n">
-        <v>14.12989921713073</v>
+        <v>14.12000959007443</v>
       </c>
       <c r="P6" t="n">
-        <v>316.7383195161498</v>
+        <v>316.7999587154088</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31680,28 +31771,28 @@
         <v>0.1291</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1074081620965582</v>
+        <v>0.1032176265357289</v>
       </c>
       <c r="J7" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K7" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004957157045685667</v>
+        <v>0.0045995117086437</v>
       </c>
       <c r="M7" t="n">
-        <v>8.867096450388297</v>
+        <v>8.863849817594573</v>
       </c>
       <c r="N7" t="n">
-        <v>124.1868994458099</v>
+        <v>123.9839473439312</v>
       </c>
       <c r="O7" t="n">
-        <v>11.14391759866385</v>
+        <v>11.13480791679548</v>
       </c>
       <c r="P7" t="n">
-        <v>331.525057383306</v>
+        <v>331.5691410837381</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31758,28 +31849,28 @@
         <v>0.1133</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4100782337282102</v>
+        <v>0.4005350826852426</v>
       </c>
       <c r="J8" t="n">
+        <v>337</v>
+      </c>
+      <c r="K8" t="n">
         <v>336</v>
       </c>
-      <c r="K8" t="n">
-        <v>335</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.05492525313548191</v>
+        <v>0.0525381325271248</v>
       </c>
       <c r="M8" t="n">
-        <v>9.692372807572797</v>
+        <v>9.711577129321746</v>
       </c>
       <c r="N8" t="n">
-        <v>155.30324337229</v>
+        <v>155.7016248289112</v>
       </c>
       <c r="O8" t="n">
-        <v>12.46207219415334</v>
+        <v>12.47804571352867</v>
       </c>
       <c r="P8" t="n">
-        <v>324.8392519974823</v>
+        <v>324.9396870139244</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31836,28 +31927,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2860514426692589</v>
+        <v>0.2764997513754203</v>
       </c>
       <c r="J9" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K9" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02465626180319658</v>
+        <v>0.02309220639408571</v>
       </c>
       <c r="M9" t="n">
-        <v>10.34154140159177</v>
+        <v>10.36282394394453</v>
       </c>
       <c r="N9" t="n">
-        <v>170.1151196191242</v>
+        <v>170.4428028784581</v>
       </c>
       <c r="O9" t="n">
-        <v>13.04281869915872</v>
+        <v>13.05537448250559</v>
       </c>
       <c r="P9" t="n">
-        <v>321.0432129636327</v>
+        <v>321.1453296311495</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31914,28 +32005,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9590323753344211</v>
+        <v>-0.9886592739815873</v>
       </c>
       <c r="J10" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K10" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04473929203719118</v>
+        <v>0.04731898119636857</v>
       </c>
       <c r="M10" t="n">
-        <v>21.1100361491314</v>
+        <v>21.30173244993058</v>
       </c>
       <c r="N10" t="n">
-        <v>1053.365902879835</v>
+        <v>1058.413477971746</v>
       </c>
       <c r="O10" t="n">
-        <v>32.45559894501772</v>
+        <v>32.53326725018172</v>
       </c>
       <c r="P10" t="n">
-        <v>331.5266176123548</v>
+        <v>331.839120674473</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31992,28 +32083,28 @@
         <v>0.0462</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.790589236513821</v>
+        <v>-0.8137213497185997</v>
       </c>
       <c r="J11" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K11" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02516585681077899</v>
+        <v>0.02668614687757676</v>
       </c>
       <c r="M11" t="n">
-        <v>26.36689991533168</v>
+        <v>26.45247755681913</v>
       </c>
       <c r="N11" t="n">
-        <v>1283.103881445448</v>
+        <v>1283.323060582161</v>
       </c>
       <c r="O11" t="n">
-        <v>35.82043943679988</v>
+        <v>35.82349872056275</v>
       </c>
       <c r="P11" t="n">
-        <v>334.4004380484868</v>
+        <v>334.6467837571527</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32070,28 +32161,28 @@
         <v>0.0351</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0008139275817609002</v>
+        <v>-0.02561294879753535</v>
       </c>
       <c r="J12" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K12" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L12" t="n">
-        <v>5.556293691810765e-08</v>
+        <v>5.477659696107029e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>20.38103546529262</v>
+        <v>20.46334668326131</v>
       </c>
       <c r="N12" t="n">
-        <v>636.9619464364263</v>
+        <v>641.5339779532562</v>
       </c>
       <c r="O12" t="n">
-        <v>25.23810504844661</v>
+        <v>25.32852103762192</v>
       </c>
       <c r="P12" t="n">
-        <v>327.7941559382105</v>
+        <v>328.0729788931517</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32148,28 +32239,28 @@
         <v>0.098</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7858249641394337</v>
+        <v>0.7652335087338433</v>
       </c>
       <c r="J13" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K13" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05029383841673163</v>
+        <v>0.04779302454242662</v>
       </c>
       <c r="M13" t="n">
-        <v>20.2379634820274</v>
+        <v>20.30306256410373</v>
       </c>
       <c r="N13" t="n">
-        <v>617.3339204129542</v>
+        <v>619.3631686592773</v>
       </c>
       <c r="O13" t="n">
-        <v>24.84620535238639</v>
+        <v>24.8870080294775</v>
       </c>
       <c r="P13" t="n">
-        <v>314.7953905397566</v>
+        <v>315.0140621828954</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32226,28 +32317,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1268312510666297</v>
+        <v>0.1113384773057137</v>
       </c>
       <c r="J14" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K14" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001515874864472799</v>
+        <v>0.001170540119318719</v>
       </c>
       <c r="M14" t="n">
-        <v>19.81316826623622</v>
+        <v>19.84461012526673</v>
       </c>
       <c r="N14" t="n">
-        <v>564.9469376742927</v>
+        <v>565.5074507088777</v>
       </c>
       <c r="O14" t="n">
-        <v>23.76861244739147</v>
+        <v>23.78040055820923</v>
       </c>
       <c r="P14" t="n">
-        <v>326.8240252780475</v>
+        <v>326.98806864115</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32304,28 +32395,28 @@
         <v>0.0863</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2472940861970221</v>
+        <v>-0.2589470855029677</v>
       </c>
       <c r="J15" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K15" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L15" t="n">
-        <v>0.005729372160193646</v>
+        <v>0.006299996773026284</v>
       </c>
       <c r="M15" t="n">
-        <v>19.71115532390857</v>
+        <v>19.72401152514739</v>
       </c>
       <c r="N15" t="n">
-        <v>565.8513175436177</v>
+        <v>565.431182535416</v>
       </c>
       <c r="O15" t="n">
-        <v>23.78762950660737</v>
+        <v>23.77879691101751</v>
       </c>
       <c r="P15" t="n">
-        <v>341.4889887424898</v>
+        <v>341.6123751177042</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32382,28 +32473,28 @@
         <v>0.0584</v>
       </c>
       <c r="I16" t="n">
-        <v>0.09731429586156355</v>
+        <v>0.09779608300067137</v>
       </c>
       <c r="J16" t="n">
+        <v>337</v>
+      </c>
+      <c r="K16" t="n">
         <v>336</v>
       </c>
-      <c r="K16" t="n">
-        <v>335</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.003287107194492433</v>
+        <v>0.003338555298546542</v>
       </c>
       <c r="M16" t="n">
-        <v>10.0162120568516</v>
+        <v>9.988584650441894</v>
       </c>
       <c r="N16" t="n">
-        <v>154.1468149743342</v>
+        <v>153.6902232852431</v>
       </c>
       <c r="O16" t="n">
-        <v>12.41558758071217</v>
+        <v>12.39718610351733</v>
       </c>
       <c r="P16" t="n">
-        <v>349.9161704872741</v>
+        <v>349.9111088294529</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32460,28 +32551,28 @@
         <v>0.061</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1856677342684385</v>
+        <v>0.1844720313525139</v>
       </c>
       <c r="J17" t="n">
+        <v>337</v>
+      </c>
+      <c r="K17" t="n">
         <v>336</v>
       </c>
-      <c r="K17" t="n">
-        <v>335</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.01559207906621984</v>
+        <v>0.01547953365673982</v>
       </c>
       <c r="M17" t="n">
-        <v>7.8339630269838</v>
+        <v>7.817391886651329</v>
       </c>
       <c r="N17" t="n">
-        <v>116.8145510428995</v>
+        <v>116.4803988655851</v>
       </c>
       <c r="O17" t="n">
-        <v>10.80807804574428</v>
+        <v>10.79260852924746</v>
       </c>
       <c r="P17" t="n">
-        <v>349.3638628366882</v>
+        <v>349.3764467768856</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32538,28 +32629,28 @@
         <v>0.0711</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2799419359746695</v>
+        <v>0.2761692335020106</v>
       </c>
       <c r="J18" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K18" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04107155855779276</v>
+        <v>0.04018216305967259</v>
       </c>
       <c r="M18" t="n">
-        <v>7.834149600436697</v>
+        <v>7.833466142158678</v>
       </c>
       <c r="N18" t="n">
-        <v>98.12350455724757</v>
+        <v>97.96652325707326</v>
       </c>
       <c r="O18" t="n">
-        <v>9.905730894651215</v>
+        <v>9.89780396133775</v>
       </c>
       <c r="P18" t="n">
-        <v>345.294976506194</v>
+        <v>345.3346646756917</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32616,28 +32707,28 @@
         <v>0.1025</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3025002687958566</v>
+        <v>0.2999966856576393</v>
       </c>
       <c r="J19" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K19" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03979786013404651</v>
+        <v>0.03936250193818247</v>
       </c>
       <c r="M19" t="n">
-        <v>8.752595358318318</v>
+        <v>8.739892841024842</v>
       </c>
       <c r="N19" t="n">
-        <v>118.7414264923462</v>
+        <v>118.4464137830927</v>
       </c>
       <c r="O19" t="n">
-        <v>10.89685397224108</v>
+        <v>10.8833089537646</v>
       </c>
       <c r="P19" t="n">
-        <v>340.0763276837658</v>
+        <v>340.1026633561836</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32694,28 +32785,28 @@
         <v>0.0791</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5260578261598885</v>
+        <v>0.5256460361888113</v>
       </c>
       <c r="J20" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K20" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L20" t="n">
-        <v>0.09254344795745217</v>
+        <v>0.09288921846920239</v>
       </c>
       <c r="M20" t="n">
-        <v>9.628846686876617</v>
+        <v>9.60247784834664</v>
       </c>
       <c r="N20" t="n">
-        <v>145.5255494304994</v>
+        <v>145.0953215295792</v>
       </c>
       <c r="O20" t="n">
-        <v>12.06339709329422</v>
+        <v>12.04555193959908</v>
       </c>
       <c r="P20" t="n">
-        <v>333.7834395550026</v>
+        <v>333.7877715134032</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32772,28 +32863,28 @@
         <v>0.1044</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5420740660221832</v>
+        <v>0.5428670648587057</v>
       </c>
       <c r="J21" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K21" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L21" t="n">
-        <v>0.09039771180588685</v>
+        <v>0.09110390968814663</v>
       </c>
       <c r="M21" t="n">
-        <v>10.30297904117994</v>
+        <v>10.27614271233457</v>
       </c>
       <c r="N21" t="n">
-        <v>159.108903443701</v>
+        <v>158.6399162801633</v>
       </c>
       <c r="O21" t="n">
-        <v>12.61383777617665</v>
+        <v>12.59523387159458</v>
       </c>
       <c r="P21" t="n">
-        <v>331.2548484777167</v>
+        <v>331.2465106846227</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32850,28 +32941,28 @@
         <v>0.1153</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5481785183553677</v>
+        <v>0.551161546013662</v>
       </c>
       <c r="J22" t="n">
+        <v>337</v>
+      </c>
+      <c r="K22" t="n">
         <v>336</v>
       </c>
-      <c r="K22" t="n">
-        <v>335</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.08846058590624117</v>
+        <v>0.08976136978746851</v>
       </c>
       <c r="M22" t="n">
-        <v>10.39486544572721</v>
+        <v>10.37802146315816</v>
       </c>
       <c r="N22" t="n">
-        <v>166.1968022583621</v>
+        <v>165.7862559499535</v>
       </c>
       <c r="O22" t="n">
-        <v>12.89173387323684</v>
+        <v>12.87580117701238</v>
       </c>
       <c r="P22" t="n">
-        <v>329.0486796327918</v>
+        <v>329.0172853448298</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32928,28 +33019,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4311729741233947</v>
+        <v>0.4384075216830973</v>
       </c>
       <c r="J23" t="n">
+        <v>337</v>
+      </c>
+      <c r="K23" t="n">
         <v>336</v>
       </c>
-      <c r="K23" t="n">
-        <v>335</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.05797580044596917</v>
+        <v>0.05996804638597664</v>
       </c>
       <c r="M23" t="n">
-        <v>10.00684207484641</v>
+        <v>10.01467489199676</v>
       </c>
       <c r="N23" t="n">
-        <v>162.1329805873243</v>
+        <v>162.1450227100423</v>
       </c>
       <c r="O23" t="n">
-        <v>12.73314496058709</v>
+        <v>12.73361781702444</v>
       </c>
       <c r="P23" t="n">
-        <v>329.1731059699352</v>
+        <v>329.096967396854</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33006,28 +33097,28 @@
         <v>0.0646</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5562200572020841</v>
+        <v>0.5643048050948073</v>
       </c>
       <c r="J24" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K24" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L24" t="n">
-        <v>0.08929340928839269</v>
+        <v>0.0918385399378161</v>
       </c>
       <c r="M24" t="n">
-        <v>10.26162351365204</v>
+        <v>10.27938526330228</v>
       </c>
       <c r="N24" t="n">
-        <v>169.2171891032497</v>
+        <v>169.3312816016715</v>
       </c>
       <c r="O24" t="n">
-        <v>13.00835074493495</v>
+        <v>13.01273536200869</v>
       </c>
       <c r="P24" t="n">
-        <v>325.9546872124048</v>
+        <v>325.8696370800295</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33065,7 +33156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y337"/>
+  <dimension ref="A1:Y338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75561,7 +75652,7 @@
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>-38.48943105129179,174.6382082220592</t>
+          <t>-38.48943165926706,174.63814208154417</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -75632,6 +75723,133 @@
       <c r="Y337" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:42+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>-38.495663612685796,174.63582644919424</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>-38.4950759983278,174.63638976492868</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>-38.494508319508796,174.6370230200206</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>-38.49379759227291,174.63715460265172</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>-38.49307214650108,174.63735849893126</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>-38.492282411451825,174.63727568565412</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>-38.49154807527432,174.6373747200877</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>-38.49084425274123,174.63745176501965</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>-38.490135077545524,174.63811055272004</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>-38.48943338078296,174.63795477892842</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>-38.488731650566365,174.6378018738311</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>-38.488022075331365,174.63759591559574</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>-38.487304688904985,174.63752657775822</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>-38.486603165745755,174.63733279491956</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>-38.48592843140662,174.6368290793077</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>-38.48522588486199,174.63678493788433</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>-38.484519894882595,174.6367975984657</t>
+        </is>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>-38.483816574102526,174.6367660277484</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>-38.48311712563301,174.63667034088854</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>-38.48241545071312,174.63661134086988</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>-38.481715041229315,174.63653131225357</t>
+        </is>
+      </c>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>-38.48101656783445,174.63641917001755</t>
+        </is>
+      </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>-38.48031591644363,174.63634291389718</t>
+        </is>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0260/nzd0260.xlsx
+++ b/data/nzd0260/nzd0260.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y338"/>
+  <dimension ref="A1:Y340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27611,7 +27611,7 @@
         <v>238.2</v>
       </c>
       <c r="K337" t="n">
-        <v>251.46</v>
+        <v>245.69</v>
       </c>
       <c r="L337" t="n">
         <v>269.72</v>
@@ -27692,7 +27692,7 @@
         <v>254.21</v>
       </c>
       <c r="K338" t="n">
-        <v>267.8</v>
+        <v>264.07</v>
       </c>
       <c r="L338" t="n">
         <v>281.14</v>
@@ -27736,6 +27736,168 @@
       <c r="Y338" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>322.95</v>
+      </c>
+      <c r="C339" t="n">
+        <v>300.16</v>
+      </c>
+      <c r="D339" t="n">
+        <v>273.02</v>
+      </c>
+      <c r="E339" t="n">
+        <v>288.07</v>
+      </c>
+      <c r="F339" t="n">
+        <v>301.75</v>
+      </c>
+      <c r="G339" t="n">
+        <v>327.01</v>
+      </c>
+      <c r="H339" t="n">
+        <v>318.4</v>
+      </c>
+      <c r="I339" t="n">
+        <v>311.68</v>
+      </c>
+      <c r="J339" t="n">
+        <v>264.87</v>
+      </c>
+      <c r="K339" t="n">
+        <v>276.56</v>
+      </c>
+      <c r="L339" t="n">
+        <v>285.67</v>
+      </c>
+      <c r="M339" t="n">
+        <v>304.8</v>
+      </c>
+      <c r="N339" t="n">
+        <v>306.3</v>
+      </c>
+      <c r="O339" t="n">
+        <v>320.38</v>
+      </c>
+      <c r="P339" t="n">
+        <v>354.16</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>352.33</v>
+      </c>
+      <c r="R339" t="n">
+        <v>344.33</v>
+      </c>
+      <c r="S339" t="n">
+        <v>340.19</v>
+      </c>
+      <c r="T339" t="n">
+        <v>345.89</v>
+      </c>
+      <c r="U339" t="n">
+        <v>347</v>
+      </c>
+      <c r="V339" t="n">
+        <v>347.89</v>
+      </c>
+      <c r="W339" t="n">
+        <v>353.36</v>
+      </c>
+      <c r="X339" t="n">
+        <v>354.84</v>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>331.9</v>
+      </c>
+      <c r="C340" t="n">
+        <v>300.96</v>
+      </c>
+      <c r="D340" t="n">
+        <v>275.92</v>
+      </c>
+      <c r="E340" t="n">
+        <v>289.77</v>
+      </c>
+      <c r="F340" t="n">
+        <v>311.58</v>
+      </c>
+      <c r="G340" t="n">
+        <v>341.28</v>
+      </c>
+      <c r="H340" t="n">
+        <v>341.41</v>
+      </c>
+      <c r="I340" t="n">
+        <v>311.68</v>
+      </c>
+      <c r="J340" t="n">
+        <v>264.87</v>
+      </c>
+      <c r="K340" t="n">
+        <v>285.4</v>
+      </c>
+      <c r="L340" t="n">
+        <v>297.15</v>
+      </c>
+      <c r="M340" t="n">
+        <v>308.66</v>
+      </c>
+      <c r="N340" t="n">
+        <v>310.13</v>
+      </c>
+      <c r="O340" t="n">
+        <v>324.82</v>
+      </c>
+      <c r="P340" t="n">
+        <v>354.51</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>352.29</v>
+      </c>
+      <c r="R340" t="n">
+        <v>345.15</v>
+      </c>
+      <c r="S340" t="n">
+        <v>340.14</v>
+      </c>
+      <c r="T340" t="n">
+        <v>344.77</v>
+      </c>
+      <c r="U340" t="n">
+        <v>345.74</v>
+      </c>
+      <c r="V340" t="n">
+        <v>345.76</v>
+      </c>
+      <c r="W340" t="n">
+        <v>351.37</v>
+      </c>
+      <c r="X340" t="n">
+        <v>353.18</v>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -27750,7 +27912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B346"/>
+  <dimension ref="A1:B348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31213,6 +31375,26 @@
       </c>
       <c r="B346" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -31381,28 +31563,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4104375380247761</v>
+        <v>-0.3989662091516698</v>
       </c>
       <c r="J2" t="n">
+        <v>339</v>
+      </c>
+      <c r="K2" t="n">
         <v>337</v>
       </c>
-      <c r="K2" t="n">
-        <v>335</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2228902978266104</v>
+        <v>0.2112246921276965</v>
       </c>
       <c r="M2" t="n">
-        <v>4.330271641096472</v>
+        <v>4.368787182210565</v>
       </c>
       <c r="N2" t="n">
-        <v>31.65166878926673</v>
+        <v>32.20637040824995</v>
       </c>
       <c r="O2" t="n">
-        <v>5.625981584511874</v>
+        <v>5.675065674355668</v>
       </c>
       <c r="P2" t="n">
-        <v>327.7793637157498</v>
+        <v>327.6580088833184</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31459,28 +31641,28 @@
         <v>0.1297</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4926459785026271</v>
+        <v>-0.4798388809650231</v>
       </c>
       <c r="J3" t="n">
+        <v>339</v>
+      </c>
+      <c r="K3" t="n">
         <v>337</v>
       </c>
-      <c r="K3" t="n">
-        <v>335</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1802607806493297</v>
+        <v>0.1723614488005872</v>
       </c>
       <c r="M3" t="n">
-        <v>5.972442369328969</v>
+        <v>6.010473876357385</v>
       </c>
       <c r="N3" t="n">
-        <v>59.47790301828248</v>
+        <v>59.90352527401167</v>
       </c>
       <c r="O3" t="n">
-        <v>7.712191842678868</v>
+        <v>7.739736770330866</v>
       </c>
       <c r="P3" t="n">
-        <v>301.849258683749</v>
+        <v>301.7138023256815</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31537,28 +31719,28 @@
         <v>0.1644</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1823022946882676</v>
+        <v>-0.1821556840620841</v>
       </c>
       <c r="J4" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K4" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01527733616225635</v>
+        <v>0.01542343624331488</v>
       </c>
       <c r="M4" t="n">
-        <v>8.40637916357506</v>
+        <v>8.364926902593558</v>
       </c>
       <c r="N4" t="n">
-        <v>114.5822683097304</v>
+        <v>113.9128452937756</v>
       </c>
       <c r="O4" t="n">
-        <v>10.70431073492032</v>
+        <v>10.67299607859834</v>
       </c>
       <c r="P4" t="n">
-        <v>279.092858782794</v>
+        <v>279.0912900020653</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31615,28 +31797,28 @@
         <v>0.1682</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1772280049570063</v>
+        <v>-0.1753502984012684</v>
       </c>
       <c r="J5" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K5" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01486159407589593</v>
+        <v>0.01471467103596491</v>
       </c>
       <c r="M5" t="n">
-        <v>7.785920562102478</v>
+        <v>7.748822129706381</v>
       </c>
       <c r="N5" t="n">
-        <v>111.0761766417885</v>
+        <v>110.435819340627</v>
       </c>
       <c r="O5" t="n">
-        <v>10.53926831624418</v>
+        <v>10.50884481475614</v>
       </c>
       <c r="P5" t="n">
-        <v>291.86064593681</v>
+        <v>291.8406387796721</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31693,28 +31875,28 @@
         <v>0.1057</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2578526751135644</v>
+        <v>-0.2616557633309218</v>
       </c>
       <c r="J6" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K6" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0176122789855836</v>
+        <v>0.01830996265737106</v>
       </c>
       <c r="M6" t="n">
-        <v>11.7433354674545</v>
+        <v>11.70105730716819</v>
       </c>
       <c r="N6" t="n">
-        <v>199.3746708237939</v>
+        <v>198.3944295570445</v>
       </c>
       <c r="O6" t="n">
-        <v>14.12000959007443</v>
+        <v>14.08525575050182</v>
       </c>
       <c r="P6" t="n">
-        <v>316.7999587154088</v>
+        <v>316.8403106687209</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31771,28 +31953,28 @@
         <v>0.1291</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1032176265357289</v>
+        <v>0.1030970114702561</v>
       </c>
       <c r="J7" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K7" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0045995117086437</v>
+        <v>0.004629943713182594</v>
       </c>
       <c r="M7" t="n">
-        <v>8.863849817594573</v>
+        <v>8.853670711500989</v>
       </c>
       <c r="N7" t="n">
-        <v>123.9839473439312</v>
+        <v>123.5528197915012</v>
       </c>
       <c r="O7" t="n">
-        <v>11.13480791679548</v>
+        <v>11.11543160617262</v>
       </c>
       <c r="P7" t="n">
-        <v>331.5691410837381</v>
+        <v>331.5703707493555</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31849,28 +32031,28 @@
         <v>0.1133</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4005350826852426</v>
+        <v>0.394484500658865</v>
       </c>
       <c r="J8" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K8" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0525381325271248</v>
+        <v>0.05129673957464886</v>
       </c>
       <c r="M8" t="n">
-        <v>9.711577129321746</v>
+        <v>9.721164119237898</v>
       </c>
       <c r="N8" t="n">
-        <v>155.7016248289112</v>
+        <v>155.7365288749025</v>
       </c>
       <c r="O8" t="n">
-        <v>12.47804571352867</v>
+        <v>12.47944425344745</v>
       </c>
       <c r="P8" t="n">
-        <v>324.9396870139244</v>
+        <v>325.0036030279762</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31927,28 +32109,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2764997513754203</v>
+        <v>0.2576753955597793</v>
       </c>
       <c r="J9" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K9" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02309220639408571</v>
+        <v>0.0201532963737594</v>
       </c>
       <c r="M9" t="n">
-        <v>10.36282394394453</v>
+        <v>10.4060103160371</v>
       </c>
       <c r="N9" t="n">
-        <v>170.4428028784581</v>
+        <v>171.054562021618</v>
       </c>
       <c r="O9" t="n">
-        <v>13.05537448250559</v>
+        <v>13.07878289527041</v>
       </c>
       <c r="P9" t="n">
-        <v>321.1453296311495</v>
+        <v>321.3475505989329</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32005,28 +32187,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9886592739815873</v>
+        <v>-1.03488104560488</v>
       </c>
       <c r="J10" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K10" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04731898119636857</v>
+        <v>0.05171017256696009</v>
       </c>
       <c r="M10" t="n">
-        <v>21.30173244993058</v>
+        <v>21.56991283615717</v>
       </c>
       <c r="N10" t="n">
-        <v>1058.413477971746</v>
+        <v>1062.079606743414</v>
       </c>
       <c r="O10" t="n">
-        <v>32.53326725018172</v>
+        <v>32.58956284983604</v>
       </c>
       <c r="P10" t="n">
-        <v>331.839120674473</v>
+        <v>332.3290625738205</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32083,28 +32265,28 @@
         <v>0.0462</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8137213497185997</v>
+        <v>-0.8559815721369894</v>
       </c>
       <c r="J11" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K11" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02668614687757676</v>
+        <v>0.02955968952331478</v>
       </c>
       <c r="M11" t="n">
-        <v>26.45247755681913</v>
+        <v>26.59160826481377</v>
       </c>
       <c r="N11" t="n">
-        <v>1283.323060582161</v>
+        <v>1285.256195999241</v>
       </c>
       <c r="O11" t="n">
-        <v>35.82349872056275</v>
+        <v>35.85046995506811</v>
       </c>
       <c r="P11" t="n">
-        <v>334.6467837571527</v>
+        <v>335.0983913758647</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32161,28 +32343,28 @@
         <v>0.0351</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.02561294879753535</v>
+        <v>-0.06604995184349176</v>
       </c>
       <c r="J12" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K12" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L12" t="n">
-        <v>5.477659696107029e-05</v>
+        <v>0.0003639268023537534</v>
       </c>
       <c r="M12" t="n">
-        <v>20.46334668326131</v>
+        <v>20.56056959776843</v>
       </c>
       <c r="N12" t="n">
-        <v>641.5339779532562</v>
+        <v>645.5014240675914</v>
       </c>
       <c r="O12" t="n">
-        <v>25.32852103762192</v>
+        <v>25.4067200572524</v>
       </c>
       <c r="P12" t="n">
-        <v>328.0729788931517</v>
+        <v>328.5016545859299</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32239,28 +32421,28 @@
         <v>0.098</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7652335087338433</v>
+        <v>0.7332820277317074</v>
       </c>
       <c r="J13" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K13" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04779302454242662</v>
+        <v>0.04422391322332664</v>
       </c>
       <c r="M13" t="n">
-        <v>20.30306256410373</v>
+        <v>20.37857631868317</v>
       </c>
       <c r="N13" t="n">
-        <v>619.3631686592773</v>
+        <v>620.3626493745647</v>
       </c>
       <c r="O13" t="n">
-        <v>24.8870080294775</v>
+        <v>24.90708030610101</v>
       </c>
       <c r="P13" t="n">
-        <v>315.0140621828954</v>
+        <v>315.3549966397147</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32317,28 +32499,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1113384773057137</v>
+        <v>0.08714461454593186</v>
       </c>
       <c r="J14" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K14" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001170540119318719</v>
+        <v>0.0007220755045888039</v>
       </c>
       <c r="M14" t="n">
-        <v>19.84461012526673</v>
+        <v>19.866781310832</v>
       </c>
       <c r="N14" t="n">
-        <v>565.5074507088777</v>
+        <v>564.911054667475</v>
       </c>
       <c r="O14" t="n">
-        <v>23.78040055820923</v>
+        <v>23.76785759523721</v>
       </c>
       <c r="P14" t="n">
-        <v>326.98806864115</v>
+        <v>327.2454816419852</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32395,28 +32577,28 @@
         <v>0.0863</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2589470855029677</v>
+        <v>-0.2726376576796719</v>
       </c>
       <c r="J15" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K15" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L15" t="n">
-        <v>0.006299996773026284</v>
+        <v>0.007047035486109965</v>
       </c>
       <c r="M15" t="n">
-        <v>19.72401152514739</v>
+        <v>19.68970436821694</v>
       </c>
       <c r="N15" t="n">
-        <v>565.431182535416</v>
+        <v>562.9751018555986</v>
       </c>
       <c r="O15" t="n">
-        <v>23.77879691101751</v>
+        <v>23.72709636376939</v>
       </c>
       <c r="P15" t="n">
-        <v>341.6123751177042</v>
+        <v>341.7580299275496</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32473,28 +32655,28 @@
         <v>0.0584</v>
       </c>
       <c r="I16" t="n">
-        <v>0.09779608300067137</v>
+        <v>0.099882229813559</v>
       </c>
       <c r="J16" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K16" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L16" t="n">
-        <v>0.003338555298546542</v>
+        <v>0.003521520495983532</v>
       </c>
       <c r="M16" t="n">
-        <v>9.988584650441894</v>
+        <v>9.938775956313378</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6902232852431</v>
+        <v>152.8014286240266</v>
       </c>
       <c r="O16" t="n">
-        <v>12.39718610351733</v>
+        <v>12.36128749863972</v>
       </c>
       <c r="P16" t="n">
-        <v>349.9111088294529</v>
+        <v>349.88908405661</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32551,28 +32733,28 @@
         <v>0.061</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1844720313525139</v>
+        <v>0.182395765178678</v>
       </c>
       <c r="J17" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K17" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01547953365673982</v>
+        <v>0.01530624933287783</v>
       </c>
       <c r="M17" t="n">
-        <v>7.817391886651329</v>
+        <v>7.782697026366834</v>
       </c>
       <c r="N17" t="n">
-        <v>116.4803988655851</v>
+        <v>115.8115490637901</v>
       </c>
       <c r="O17" t="n">
-        <v>10.79260852924746</v>
+        <v>10.76157744309774</v>
       </c>
       <c r="P17" t="n">
-        <v>349.3764467768856</v>
+        <v>349.3984050053779</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32629,28 +32811,28 @@
         <v>0.0711</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2761692335020106</v>
+        <v>0.2675335655797493</v>
       </c>
       <c r="J18" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K18" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04018216305967259</v>
+        <v>0.03808606730028641</v>
       </c>
       <c r="M18" t="n">
-        <v>7.833466142158678</v>
+        <v>7.838467989769567</v>
       </c>
       <c r="N18" t="n">
-        <v>97.96652325707326</v>
+        <v>97.74133996021455</v>
       </c>
       <c r="O18" t="n">
-        <v>9.89780396133775</v>
+        <v>9.886421999905453</v>
       </c>
       <c r="P18" t="n">
-        <v>345.3346646756917</v>
+        <v>345.4259501453101</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32707,28 +32889,28 @@
         <v>0.1025</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2999966856576393</v>
+        <v>0.291399040714772</v>
       </c>
       <c r="J19" t="n">
+        <v>339</v>
+      </c>
+      <c r="K19" t="n">
         <v>337</v>
       </c>
-      <c r="K19" t="n">
-        <v>335</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.03936250193818247</v>
+        <v>0.03752323609191321</v>
       </c>
       <c r="M19" t="n">
-        <v>8.739892841024842</v>
+        <v>8.733443523083945</v>
       </c>
       <c r="N19" t="n">
-        <v>118.4464137830927</v>
+        <v>118.0941682298127</v>
       </c>
       <c r="O19" t="n">
-        <v>10.8833089537646</v>
+        <v>10.86711407089355</v>
       </c>
       <c r="P19" t="n">
-        <v>340.1026633561836</v>
+        <v>340.1935481836072</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32785,28 +32967,28 @@
         <v>0.0791</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5256460361888113</v>
+        <v>0.5232602406672763</v>
       </c>
       <c r="J20" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K20" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L20" t="n">
-        <v>0.09288921846920239</v>
+        <v>0.09306633906915018</v>
       </c>
       <c r="M20" t="n">
-        <v>9.60247784834664</v>
+        <v>9.558391255953683</v>
       </c>
       <c r="N20" t="n">
-        <v>145.0953215295792</v>
+        <v>144.2680003651156</v>
       </c>
       <c r="O20" t="n">
-        <v>12.04555193959908</v>
+        <v>12.01116149109301</v>
       </c>
       <c r="P20" t="n">
-        <v>333.7877715134032</v>
+        <v>333.8129954469263</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32863,28 +33045,28 @@
         <v>0.1044</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5428670648587057</v>
+        <v>0.5439513993850685</v>
       </c>
       <c r="J21" t="n">
+        <v>339</v>
+      </c>
+      <c r="K21" t="n">
         <v>337</v>
       </c>
-      <c r="K21" t="n">
-        <v>335</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.09110390968814663</v>
+        <v>0.09237938683899949</v>
       </c>
       <c r="M21" t="n">
-        <v>10.27614271233457</v>
+        <v>10.22043287401156</v>
       </c>
       <c r="N21" t="n">
-        <v>158.6399162801633</v>
+        <v>157.7063965323622</v>
       </c>
       <c r="O21" t="n">
-        <v>12.59523387159458</v>
+        <v>12.55812074047555</v>
       </c>
       <c r="P21" t="n">
-        <v>331.2465106846227</v>
+        <v>331.2350577470845</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32941,28 +33123,28 @@
         <v>0.1153</v>
       </c>
       <c r="I22" t="n">
-        <v>0.551161546013662</v>
+        <v>0.5549850151157247</v>
       </c>
       <c r="J22" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K22" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08976136978746851</v>
+        <v>0.09180386968870657</v>
       </c>
       <c r="M22" t="n">
-        <v>10.37802146315816</v>
+        <v>10.33439011160586</v>
       </c>
       <c r="N22" t="n">
-        <v>165.7862559499535</v>
+        <v>164.8812018576247</v>
       </c>
       <c r="O22" t="n">
-        <v>12.87580117701238</v>
+        <v>12.84060753459994</v>
       </c>
       <c r="P22" t="n">
-        <v>329.0172853448298</v>
+        <v>328.9768561018734</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33019,28 +33201,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4384075216830973</v>
+        <v>0.4515465443406592</v>
       </c>
       <c r="J23" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K23" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L23" t="n">
-        <v>0.05996804638597664</v>
+        <v>0.06375972062497914</v>
       </c>
       <c r="M23" t="n">
-        <v>10.01467489199676</v>
+        <v>10.02334882399979</v>
       </c>
       <c r="N23" t="n">
-        <v>162.1450227100423</v>
+        <v>162.0078032172256</v>
       </c>
       <c r="O23" t="n">
-        <v>12.73361781702444</v>
+        <v>12.72822859698967</v>
       </c>
       <c r="P23" t="n">
-        <v>329.096967396854</v>
+        <v>328.9580186775149</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33097,28 +33279,28 @@
         <v>0.0646</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5643048050948073</v>
+        <v>0.5792045009691545</v>
       </c>
       <c r="J24" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K24" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0918385399378161</v>
+        <v>0.09673003758886267</v>
       </c>
       <c r="M24" t="n">
-        <v>10.27938526330228</v>
+        <v>10.30756495432161</v>
       </c>
       <c r="N24" t="n">
-        <v>169.3312816016715</v>
+        <v>169.3837394236069</v>
       </c>
       <c r="O24" t="n">
-        <v>13.01273536200869</v>
+        <v>13.01475083985886</v>
       </c>
       <c r="P24" t="n">
-        <v>325.8696370800295</v>
+        <v>325.7121370038116</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33156,7 +33338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y338"/>
+  <dimension ref="A1:Y340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75652,7 +75834,7 @@
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>-38.48943165926706,174.63814208154417</t>
+          <t>-38.48943105129179,174.6382082220592</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -75779,7 +75961,7 @@
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>-38.48943338078296,174.63795477892842</t>
+          <t>-38.48943298783171,174.63799753528002</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -75850,6 +76032,260 @@
       <c r="Y338" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>-38.4956642887342,174.63582882017604</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>-38.4950763670766,174.63639105818297</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>-38.49450180504448,174.6370001726682</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-38.49379759227291,174.63715460265172</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>-38.49306726516102,174.63733714326855</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>-38.492282228318345,174.6372734047122</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>-38.49154807527432,174.6373747200877</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>-38.49084425274123,174.63745176501965</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>-38.49013620066176,174.6379883577818</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>-38.4894343035776,174.63785436454373</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>-38.488732127699045,174.63774994771532</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>-38.48802350100647,174.6375305994527</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>-38.487306715614615,174.63748389755855</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>-38.486607335630936,174.6372638759202</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>-38.485929026077024,174.63681925015064</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>-38.48522608538923,174.6367816234332</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>-38.48451887149882,174.63681451343004</t>
+        </is>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>-38.483814319898954,174.6368032860244</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>-38.48311656554808,174.6366795982247</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>-38.48241563049184,174.63660836940784</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>-38.48171453647127,174.63653965512455</t>
+        </is>
+      </c>
+      <c r="W339" t="inlineStr">
+        <is>
+          <t>-38.48101660240637,174.63641859859348</t>
+        </is>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>-38.480315902615,174.63634314246463</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>-38.495636785816394,174.63573236436142</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>-38.495073908751,174.63638243648796</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>-38.49449289374157,174.6369689192209</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>-38.49379236841048,174.6371362818419</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>-38.493042531299686,174.63722893394777</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>-38.49226916162927,174.63711065953166</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>-38.491550497836045,174.63711095259586</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>-38.49084425274123,174.63745176501965</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>-38.49013620066176,174.6379883577818</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>-38.48943523471235,174.63775303312693</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>-38.488733336753384,174.63761835569773</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>-38.48802446644297,174.63748636781685</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>-38.48730879664348,174.63744007311456</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>-38.48661040596833,174.6372131295863</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>-38.48592926809381,174.63681524991225</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>-38.48522605773031,174.63678208059886</t>
+        </is>
+      </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>-38.48451943850906,174.63680514162556</t>
+        </is>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>-38.48381428532518,174.63680385747028</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>-38.48311579110847,174.6366923984917</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>-38.48241475925584,174.63662276956984</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>-38.481713063680665,174.63656399802127</t>
+        </is>
+      </c>
+      <c r="W340" t="inlineStr">
+        <is>
+          <t>-38.48101522644237,174.6364413412714</t>
+        </is>
+      </c>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>-38.48031475483836,174.63636211356163</t>
+        </is>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0260/nzd0260.xlsx
+++ b/data/nzd0260/nzd0260.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y340"/>
+  <dimension ref="A1:Y341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27827,7 +27827,7 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>331.9</v>
+        <v>322.95</v>
       </c>
       <c r="C340" t="n">
         <v>300.96</v>
@@ -27839,13 +27839,13 @@
         <v>289.77</v>
       </c>
       <c r="F340" t="n">
-        <v>311.58</v>
+        <v>301.75</v>
       </c>
       <c r="G340" t="n">
-        <v>341.28</v>
+        <v>327.01</v>
       </c>
       <c r="H340" t="n">
-        <v>341.41</v>
+        <v>318.4</v>
       </c>
       <c r="I340" t="n">
         <v>311.68</v>
@@ -27898,6 +27898,87 @@
       <c r="Y340" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>327.34</v>
+      </c>
+      <c r="C341" t="n">
+        <v>303.48</v>
+      </c>
+      <c r="D341" t="n">
+        <v>285.55</v>
+      </c>
+      <c r="E341" t="n">
+        <v>294.4</v>
+      </c>
+      <c r="F341" t="n">
+        <v>310.09</v>
+      </c>
+      <c r="G341" t="n">
+        <v>328.13</v>
+      </c>
+      <c r="H341" t="n">
+        <v>316.86</v>
+      </c>
+      <c r="I341" t="n">
+        <v>311.22</v>
+      </c>
+      <c r="J341" t="n">
+        <v>295.16</v>
+      </c>
+      <c r="K341" t="n">
+        <v>313.11</v>
+      </c>
+      <c r="L341" t="n">
+        <v>317.34</v>
+      </c>
+      <c r="M341" t="n">
+        <v>326.61</v>
+      </c>
+      <c r="N341" t="n">
+        <v>331.54</v>
+      </c>
+      <c r="O341" t="n">
+        <v>338.57</v>
+      </c>
+      <c r="P341" t="n">
+        <v>356.42</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>353.25</v>
+      </c>
+      <c r="R341" t="n">
+        <v>349.18</v>
+      </c>
+      <c r="S341" t="n">
+        <v>342.05</v>
+      </c>
+      <c r="T341" t="n">
+        <v>344.9</v>
+      </c>
+      <c r="U341" t="n">
+        <v>344.54</v>
+      </c>
+      <c r="V341" t="n">
+        <v>340.55</v>
+      </c>
+      <c r="W341" t="n">
+        <v>346.42</v>
+      </c>
+      <c r="X341" t="n">
+        <v>348.78</v>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -27912,7 +27993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B348"/>
+  <dimension ref="A1:B349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31395,6 +31476,16 @@
       </c>
       <c r="B348" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -31563,28 +31654,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3989662091516698</v>
+        <v>-0.3982980092900509</v>
       </c>
       <c r="J2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K2" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2112246921276965</v>
+        <v>0.2128473426362527</v>
       </c>
       <c r="M2" t="n">
-        <v>4.368787182210565</v>
+        <v>4.359478086908375</v>
       </c>
       <c r="N2" t="n">
-        <v>32.20637040824995</v>
+        <v>31.87445207935803</v>
       </c>
       <c r="O2" t="n">
-        <v>5.675065674355668</v>
+        <v>5.645746370441913</v>
       </c>
       <c r="P2" t="n">
-        <v>327.6580088833184</v>
+        <v>327.6507437078729</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31641,28 +31732,28 @@
         <v>0.1297</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4798388809650231</v>
+        <v>-0.4719133803018516</v>
       </c>
       <c r="J3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1723614488005872</v>
+        <v>0.1670574838330888</v>
       </c>
       <c r="M3" t="n">
-        <v>6.010473876357385</v>
+        <v>6.038521564679781</v>
       </c>
       <c r="N3" t="n">
-        <v>59.90352527401167</v>
+        <v>60.32667649498232</v>
       </c>
       <c r="O3" t="n">
-        <v>7.739736770330866</v>
+        <v>7.767024944918248</v>
       </c>
       <c r="P3" t="n">
-        <v>301.7138023256815</v>
+        <v>301.629659940564</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31719,28 +31810,28 @@
         <v>0.1644</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1821556840620841</v>
+        <v>-0.1759029746682836</v>
       </c>
       <c r="J4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K4" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01542343624331488</v>
+        <v>0.01443220484058916</v>
       </c>
       <c r="M4" t="n">
-        <v>8.364926902593558</v>
+        <v>8.371163772935235</v>
       </c>
       <c r="N4" t="n">
-        <v>113.9128452937756</v>
+        <v>113.9449663574004</v>
       </c>
       <c r="O4" t="n">
-        <v>10.67299607859834</v>
+        <v>10.67450075448029</v>
       </c>
       <c r="P4" t="n">
-        <v>279.0912900020653</v>
+        <v>279.0245321817537</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31797,28 +31888,28 @@
         <v>0.1682</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1753502984012684</v>
+        <v>-0.1713600367286658</v>
       </c>
       <c r="J5" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K5" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01471467103596491</v>
+        <v>0.01412203956514624</v>
       </c>
       <c r="M5" t="n">
-        <v>7.748822129706381</v>
+        <v>7.74526161586168</v>
       </c>
       <c r="N5" t="n">
-        <v>110.435819340627</v>
+        <v>110.258192726475</v>
       </c>
       <c r="O5" t="n">
-        <v>10.50884481475614</v>
+        <v>10.50039012258473</v>
       </c>
       <c r="P5" t="n">
-        <v>291.8406387796721</v>
+        <v>291.7979735921456</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31875,28 +31966,28 @@
         <v>0.1057</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2616557633309218</v>
+        <v>-0.2670471226543716</v>
       </c>
       <c r="J6" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K6" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01830996265737106</v>
+        <v>0.01914545570464499</v>
       </c>
       <c r="M6" t="n">
-        <v>11.70105730716819</v>
+        <v>11.68417377706203</v>
       </c>
       <c r="N6" t="n">
-        <v>198.3944295570445</v>
+        <v>197.9967553692213</v>
       </c>
       <c r="O6" t="n">
-        <v>14.08525575050182</v>
+        <v>14.07113198606357</v>
       </c>
       <c r="P6" t="n">
-        <v>316.8403106687209</v>
+        <v>316.8975882068293</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31953,28 +32044,28 @@
         <v>0.1291</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1030970114702561</v>
+        <v>0.09184739485936742</v>
       </c>
       <c r="J7" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K7" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004629943713182594</v>
+        <v>0.003695778999979416</v>
       </c>
       <c r="M7" t="n">
-        <v>8.853670711500989</v>
+        <v>8.847409883140704</v>
       </c>
       <c r="N7" t="n">
-        <v>123.5528197915012</v>
+        <v>123.2994552058077</v>
       </c>
       <c r="O7" t="n">
-        <v>11.11543160617262</v>
+        <v>11.10402878264496</v>
       </c>
       <c r="P7" t="n">
-        <v>331.5703707493555</v>
+        <v>331.6894690466788</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32031,28 +32122,28 @@
         <v>0.1133</v>
       </c>
       <c r="I8" t="n">
-        <v>0.394484500658865</v>
+        <v>0.3716027909677195</v>
       </c>
       <c r="J8" t="n">
+        <v>340</v>
+      </c>
+      <c r="K8" t="n">
         <v>339</v>
       </c>
-      <c r="K8" t="n">
-        <v>338</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.05129673957464886</v>
+        <v>0.04555843560343775</v>
       </c>
       <c r="M8" t="n">
-        <v>9.721164119237898</v>
+        <v>9.774217244767238</v>
       </c>
       <c r="N8" t="n">
-        <v>155.7365288749025</v>
+        <v>156.9679100860175</v>
       </c>
       <c r="O8" t="n">
-        <v>12.47944425344745</v>
+        <v>12.5286834937282</v>
       </c>
       <c r="P8" t="n">
-        <v>325.0036030279762</v>
+        <v>325.2460725249258</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32109,28 +32200,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2576753955597793</v>
+        <v>0.2481653098028561</v>
       </c>
       <c r="J9" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K9" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0201532963737594</v>
+        <v>0.01873540720236289</v>
       </c>
       <c r="M9" t="n">
-        <v>10.4060103160371</v>
+        <v>10.42886946141109</v>
       </c>
       <c r="N9" t="n">
-        <v>171.054562021618</v>
+        <v>171.3837918022237</v>
       </c>
       <c r="O9" t="n">
-        <v>13.07878289527041</v>
+        <v>13.09136325224473</v>
       </c>
       <c r="P9" t="n">
-        <v>321.3475505989329</v>
+        <v>321.4500942646804</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32187,28 +32278,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.03488104560488</v>
+        <v>-1.040551732407809</v>
       </c>
       <c r="J10" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K10" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05171017256696009</v>
+        <v>0.05251822502170345</v>
       </c>
       <c r="M10" t="n">
-        <v>21.56991283615717</v>
+        <v>21.55358564388974</v>
       </c>
       <c r="N10" t="n">
-        <v>1062.079606743414</v>
+        <v>1059.203894440834</v>
       </c>
       <c r="O10" t="n">
-        <v>32.58956284983604</v>
+        <v>32.54541280181945</v>
       </c>
       <c r="P10" t="n">
-        <v>332.3290625738205</v>
+        <v>332.3893995385479</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32265,28 +32356,28 @@
         <v>0.0462</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8559815721369894</v>
+        <v>-0.8557649293157844</v>
       </c>
       <c r="J11" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K11" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02955968952331478</v>
+        <v>0.02971071982670315</v>
       </c>
       <c r="M11" t="n">
-        <v>26.59160826481377</v>
+        <v>26.51203785483569</v>
       </c>
       <c r="N11" t="n">
-        <v>1285.256195999241</v>
+        <v>1281.37368218086</v>
       </c>
       <c r="O11" t="n">
-        <v>35.85046995506811</v>
+        <v>35.79628028414209</v>
       </c>
       <c r="P11" t="n">
-        <v>335.0983913758647</v>
+        <v>335.0960653115789</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32343,28 +32434,28 @@
         <v>0.0351</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.06604995184349176</v>
+        <v>-0.07134184663240149</v>
       </c>
       <c r="J12" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K12" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0003639268023537534</v>
+        <v>0.0004268249505259281</v>
       </c>
       <c r="M12" t="n">
-        <v>20.56056959776843</v>
+        <v>20.52827526856787</v>
       </c>
       <c r="N12" t="n">
-        <v>645.5014240675914</v>
+        <v>643.8426888409384</v>
       </c>
       <c r="O12" t="n">
-        <v>25.4067200572524</v>
+        <v>25.37405542756101</v>
       </c>
       <c r="P12" t="n">
-        <v>328.5016545859299</v>
+        <v>328.5579702236384</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32421,28 +32512,28 @@
         <v>0.098</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7332820277317074</v>
+        <v>0.7288092250100728</v>
       </c>
       <c r="J13" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K13" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04422391322332664</v>
+        <v>0.04393870501139985</v>
       </c>
       <c r="M13" t="n">
-        <v>20.37857631868317</v>
+        <v>20.34524903769911</v>
       </c>
       <c r="N13" t="n">
-        <v>620.3626493745647</v>
+        <v>618.6959689257098</v>
       </c>
       <c r="O13" t="n">
-        <v>24.90708030610101</v>
+        <v>24.87359983849764</v>
       </c>
       <c r="P13" t="n">
-        <v>315.3549966397147</v>
+        <v>315.4029031887647</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32499,28 +32590,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08714461454593186</v>
+        <v>0.08826794358559638</v>
       </c>
       <c r="J14" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K14" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0007220755045888039</v>
+        <v>0.0007449983297722618</v>
       </c>
       <c r="M14" t="n">
-        <v>19.866781310832</v>
+        <v>19.81317433133425</v>
       </c>
       <c r="N14" t="n">
-        <v>564.911054667475</v>
+        <v>563.2466999718819</v>
       </c>
       <c r="O14" t="n">
-        <v>23.76785759523721</v>
+        <v>23.73281904814263</v>
       </c>
       <c r="P14" t="n">
-        <v>327.2454816419852</v>
+        <v>327.2334840979381</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32577,28 +32668,28 @@
         <v>0.0863</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2726376576796719</v>
+        <v>-0.2704445230832961</v>
       </c>
       <c r="J15" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K15" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L15" t="n">
-        <v>0.007047035486109965</v>
+        <v>0.006973567717858176</v>
       </c>
       <c r="M15" t="n">
-        <v>19.68970436821694</v>
+        <v>19.64125590228717</v>
       </c>
       <c r="N15" t="n">
-        <v>562.9751018555986</v>
+        <v>561.3500611532467</v>
       </c>
       <c r="O15" t="n">
-        <v>23.72709636376939</v>
+        <v>23.6928272089518</v>
       </c>
       <c r="P15" t="n">
-        <v>341.7580299275496</v>
+        <v>341.734606488831</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32655,28 +32746,28 @@
         <v>0.0584</v>
       </c>
       <c r="I16" t="n">
-        <v>0.099882229813559</v>
+        <v>0.1020587841185385</v>
       </c>
       <c r="J16" t="n">
+        <v>340</v>
+      </c>
+      <c r="K16" t="n">
         <v>339</v>
       </c>
-      <c r="K16" t="n">
-        <v>338</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.003521520495983532</v>
+        <v>0.003696006400333851</v>
       </c>
       <c r="M16" t="n">
-        <v>9.938775956313378</v>
+        <v>9.919060803394467</v>
       </c>
       <c r="N16" t="n">
-        <v>152.8014286240266</v>
+        <v>152.3955487209251</v>
       </c>
       <c r="O16" t="n">
-        <v>12.36128749863972</v>
+        <v>12.34485920215071</v>
       </c>
       <c r="P16" t="n">
-        <v>349.88908405661</v>
+        <v>349.8660194295571</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32733,28 +32824,28 @@
         <v>0.061</v>
       </c>
       <c r="I17" t="n">
-        <v>0.182395765178678</v>
+        <v>0.1818892368597373</v>
       </c>
       <c r="J17" t="n">
+        <v>340</v>
+      </c>
+      <c r="K17" t="n">
         <v>339</v>
       </c>
-      <c r="K17" t="n">
-        <v>338</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.01530624933287783</v>
+        <v>0.01530766292914576</v>
       </c>
       <c r="M17" t="n">
-        <v>7.782697026366834</v>
+        <v>7.762531373955273</v>
       </c>
       <c r="N17" t="n">
-        <v>115.8115490637901</v>
+        <v>115.4723674119761</v>
       </c>
       <c r="O17" t="n">
-        <v>10.76157744309774</v>
+        <v>10.74580696885888</v>
       </c>
       <c r="P17" t="n">
-        <v>349.3984050053779</v>
+        <v>349.4037821974353</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32811,28 +32902,28 @@
         <v>0.0711</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2675335655797493</v>
+        <v>0.2657406239553695</v>
       </c>
       <c r="J18" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K18" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03808606730028641</v>
+        <v>0.03779126356590223</v>
       </c>
       <c r="M18" t="n">
-        <v>7.838467989769567</v>
+        <v>7.825966489482735</v>
       </c>
       <c r="N18" t="n">
-        <v>97.74133996021455</v>
+        <v>97.48443506788328</v>
       </c>
       <c r="O18" t="n">
-        <v>9.886421999905453</v>
+        <v>9.873420636632639</v>
       </c>
       <c r="P18" t="n">
-        <v>345.4259501453101</v>
+        <v>345.444974856434</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32889,28 +32980,28 @@
         <v>0.1025</v>
       </c>
       <c r="I19" t="n">
-        <v>0.291399040714772</v>
+        <v>0.2882090095095238</v>
       </c>
       <c r="J19" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K19" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03752323609191321</v>
+        <v>0.03690792884893079</v>
       </c>
       <c r="M19" t="n">
-        <v>8.733443523083945</v>
+        <v>8.724289764508583</v>
       </c>
       <c r="N19" t="n">
-        <v>118.0941682298127</v>
+        <v>117.8421029554334</v>
       </c>
       <c r="O19" t="n">
-        <v>10.86711407089355</v>
+        <v>10.85551025771858</v>
       </c>
       <c r="P19" t="n">
-        <v>340.1935481836072</v>
+        <v>340.2273978436512</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32967,28 +33058,28 @@
         <v>0.0791</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5232602406672763</v>
+        <v>0.5218290610950298</v>
       </c>
       <c r="J20" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K20" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L20" t="n">
-        <v>0.09306633906915018</v>
+        <v>0.09307242465678078</v>
       </c>
       <c r="M20" t="n">
-        <v>9.558391255953683</v>
+        <v>9.537739161970906</v>
       </c>
       <c r="N20" t="n">
-        <v>144.2680003651156</v>
+        <v>143.8631608011951</v>
       </c>
       <c r="O20" t="n">
-        <v>12.01116149109301</v>
+        <v>11.99429701154658</v>
       </c>
       <c r="P20" t="n">
-        <v>333.8129954469263</v>
+        <v>333.8281815397461</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33045,28 +33136,28 @@
         <v>0.1044</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5439513993850685</v>
+        <v>0.5434476311279818</v>
       </c>
       <c r="J21" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K21" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L21" t="n">
-        <v>0.09237938683899949</v>
+        <v>0.09269862806575435</v>
       </c>
       <c r="M21" t="n">
-        <v>10.22043287401156</v>
+        <v>10.19310945317906</v>
       </c>
       <c r="N21" t="n">
-        <v>157.7063965323622</v>
+        <v>157.2422373466597</v>
       </c>
       <c r="O21" t="n">
-        <v>12.55812074047555</v>
+        <v>12.53962668290646</v>
       </c>
       <c r="P21" t="n">
-        <v>331.2350577470845</v>
+        <v>331.2404007692531</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33123,28 +33214,28 @@
         <v>0.1153</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5549850151157247</v>
+        <v>0.5533648097958701</v>
       </c>
       <c r="J22" t="n">
+        <v>340</v>
+      </c>
+      <c r="K22" t="n">
         <v>339</v>
       </c>
-      <c r="K22" t="n">
-        <v>338</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.09180386968870657</v>
+        <v>0.09177697653300043</v>
       </c>
       <c r="M22" t="n">
-        <v>10.33439011160586</v>
+        <v>10.31356597035258</v>
       </c>
       <c r="N22" t="n">
-        <v>164.8812018576247</v>
+        <v>164.41984570824</v>
       </c>
       <c r="O22" t="n">
-        <v>12.84060753459994</v>
+        <v>12.82263021802626</v>
       </c>
       <c r="P22" t="n">
-        <v>328.9768561018734</v>
+        <v>328.9940558414563</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33201,28 +33292,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4515465443406592</v>
+        <v>0.4546827248924841</v>
       </c>
       <c r="J23" t="n">
+        <v>340</v>
+      </c>
+      <c r="K23" t="n">
         <v>339</v>
       </c>
-      <c r="K23" t="n">
-        <v>338</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.06375972062497914</v>
+        <v>0.06489968831015858</v>
       </c>
       <c r="M23" t="n">
-        <v>10.02334882399979</v>
+        <v>10.00989876362197</v>
       </c>
       <c r="N23" t="n">
-        <v>162.0078032172256</v>
+        <v>161.6236458944387</v>
       </c>
       <c r="O23" t="n">
-        <v>12.72822859698967</v>
+        <v>12.71312887901474</v>
       </c>
       <c r="P23" t="n">
-        <v>328.9580186775149</v>
+        <v>328.9247256817967</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33279,28 +33370,28 @@
         <v>0.0646</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5792045009691545</v>
+        <v>0.5835998315894793</v>
       </c>
       <c r="J24" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K24" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L24" t="n">
-        <v>0.09673003758886267</v>
+        <v>0.09846660500933957</v>
       </c>
       <c r="M24" t="n">
-        <v>10.30756495432161</v>
+        <v>10.30328155291773</v>
       </c>
       <c r="N24" t="n">
-        <v>169.3837394236069</v>
+        <v>169.0692654579721</v>
       </c>
       <c r="O24" t="n">
-        <v>13.01475083985886</v>
+        <v>13.00266378316275</v>
       </c>
       <c r="P24" t="n">
-        <v>325.7121370038116</v>
+        <v>325.6654986223892</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33338,7 +33429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y340"/>
+  <dimension ref="A1:Y341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76170,7 +76261,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>-38.495636785816394,174.63573236436142</t>
+          <t>-38.4956642887342,174.63582882017604</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -76190,17 +76281,17 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>-38.493042531299686,174.63722893394777</t>
+          <t>-38.49306726516102,174.63733714326855</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>-38.49226916162927,174.63711065953166</t>
+          <t>-38.492282228318345,174.6372734047122</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>-38.491550497836045,174.63711095259586</t>
+          <t>-38.49154807527432,174.6373747200877</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -76286,6 +76377,133 @@
       <c r="Y340" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-38.495650798486345,174.6357815083207</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>-38.495066165021136,174.63635527815248</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-38.494463302009024,174.63686513627516</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-38.49377814105266,174.6370863845904</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-38.49304628038592,174.6372453359664</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>-38.49228120277003,174.6372606314376</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-38.491547913117294,174.63739237336478</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>-38.49084420430244,174.637457038025</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>-38.490139391259824,174.6376411452897</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>-38.48943815289364,174.63743539807157</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>-38.488735462771736,174.63738692337137</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>-38.488028955753656,174.63728067922756</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>-38.48732042945675,174.6371950909826</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>-38.48661991419407,174.6370559759299</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>-38.48593058881158,174.63679342003928</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>-38.48522672154402,174.6367711086225</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>-38.48452222514603,174.63675908263266</t>
+        </is>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>-38.48381560604109,174.63678202823536</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>-38.48311588099886,174.63669091274645</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>-38.482413929505626,174.63663648400944</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>-38.48170946119976,174.6366235409703</t>
+        </is>
+      </c>
+      <c r="W341" t="inlineStr">
+        <is>
+          <t>-38.48101180379931,174.6364979122496</t>
+        </is>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>-38.480311712524006,174.63641239839356</t>
+        </is>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0260/nzd0260.xlsx
+++ b/data/nzd0260/nzd0260.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y341"/>
+  <dimension ref="A1:Y342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27977,6 +27977,87 @@
         <v>348.78</v>
       </c>
       <c r="Y341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>331.24</v>
+      </c>
+      <c r="C342" t="n">
+        <v>306.94</v>
+      </c>
+      <c r="D342" t="n">
+        <v>292.14</v>
+      </c>
+      <c r="E342" t="n">
+        <v>295.65</v>
+      </c>
+      <c r="F342" t="n">
+        <v>313.7</v>
+      </c>
+      <c r="G342" t="n">
+        <v>329.12</v>
+      </c>
+      <c r="H342" t="n">
+        <v>317.72</v>
+      </c>
+      <c r="I342" t="n">
+        <v>313.96</v>
+      </c>
+      <c r="J342" t="n">
+        <v>311.19</v>
+      </c>
+      <c r="K342" t="n">
+        <v>329.99</v>
+      </c>
+      <c r="L342" t="n">
+        <v>325.99</v>
+      </c>
+      <c r="M342" t="n">
+        <v>330.6</v>
+      </c>
+      <c r="N342" t="n">
+        <v>331.54</v>
+      </c>
+      <c r="O342" t="n">
+        <v>339.03</v>
+      </c>
+      <c r="P342" t="n">
+        <v>354.74</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>354.69</v>
+      </c>
+      <c r="R342" t="n">
+        <v>350.83</v>
+      </c>
+      <c r="S342" t="n">
+        <v>342.92</v>
+      </c>
+      <c r="T342" t="n">
+        <v>343.1</v>
+      </c>
+      <c r="U342" t="n">
+        <v>344.18</v>
+      </c>
+      <c r="V342" t="n">
+        <v>340.87</v>
+      </c>
+      <c r="W342" t="n">
+        <v>345.79</v>
+      </c>
+      <c r="X342" t="n">
+        <v>346.23</v>
+      </c>
+      <c r="Y342" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27993,7 +28074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B349"/>
+  <dimension ref="A1:B350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31486,6 +31567,16 @@
       </c>
       <c r="B349" t="n">
         <v>-0.5</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>-0.39</v>
       </c>
     </row>
   </sheetData>
@@ -31654,28 +31745,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3982980092900509</v>
+        <v>-0.3905695832892048</v>
       </c>
       <c r="J2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2128473426362527</v>
+        <v>0.2043558067326735</v>
       </c>
       <c r="M2" t="n">
-        <v>4.359478086908375</v>
+        <v>4.39054258206874</v>
       </c>
       <c r="N2" t="n">
-        <v>31.87445207935803</v>
+        <v>32.35457754493281</v>
       </c>
       <c r="O2" t="n">
-        <v>5.645746370441913</v>
+        <v>5.688108432944365</v>
       </c>
       <c r="P2" t="n">
-        <v>327.6507437078729</v>
+        <v>327.5685166185553</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31732,28 +31823,28 @@
         <v>0.1297</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4719133803018516</v>
+        <v>-0.4621705845832127</v>
       </c>
       <c r="J3" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1670574838330888</v>
+        <v>0.1600636764157114</v>
       </c>
       <c r="M3" t="n">
-        <v>6.038521564679781</v>
+        <v>6.077047700410667</v>
       </c>
       <c r="N3" t="n">
-        <v>60.32667649498232</v>
+        <v>61.06117523093619</v>
       </c>
       <c r="O3" t="n">
-        <v>7.767024944918248</v>
+        <v>7.814165037349555</v>
       </c>
       <c r="P3" t="n">
-        <v>301.629659940564</v>
+        <v>301.526000834082</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31810,28 +31901,28 @@
         <v>0.1644</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1759029746682836</v>
+        <v>-0.1660672638412339</v>
       </c>
       <c r="J4" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01443220484058916</v>
+        <v>0.01285292924570625</v>
       </c>
       <c r="M4" t="n">
-        <v>8.371163772935235</v>
+        <v>8.395751691323193</v>
       </c>
       <c r="N4" t="n">
-        <v>113.9449663574004</v>
+        <v>114.5289608497657</v>
       </c>
       <c r="O4" t="n">
-        <v>10.67450075448029</v>
+        <v>10.70182044559549</v>
       </c>
       <c r="P4" t="n">
-        <v>279.0245321817537</v>
+        <v>278.9192945693093</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31888,28 +31979,28 @@
         <v>0.1682</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1713600367286658</v>
+        <v>-0.1667232352322437</v>
       </c>
       <c r="J5" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K5" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01412203956514624</v>
+        <v>0.01342874108194447</v>
       </c>
       <c r="M5" t="n">
-        <v>7.74526161586168</v>
+        <v>7.745130047972032</v>
       </c>
       <c r="N5" t="n">
-        <v>110.258192726475</v>
+        <v>110.1357934525682</v>
       </c>
       <c r="O5" t="n">
-        <v>10.50039012258473</v>
+        <v>10.49456018385565</v>
       </c>
       <c r="P5" t="n">
-        <v>291.7979735921456</v>
+        <v>291.7482893050079</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31966,28 +32057,28 @@
         <v>0.1057</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2670471226543716</v>
+        <v>-0.2649450888638328</v>
       </c>
       <c r="J6" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K6" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01914545570464499</v>
+        <v>0.01895163343695705</v>
       </c>
       <c r="M6" t="n">
-        <v>11.68417377706203</v>
+        <v>11.6614515988144</v>
       </c>
       <c r="N6" t="n">
-        <v>197.9967553692213</v>
+        <v>197.4498765774626</v>
       </c>
       <c r="O6" t="n">
-        <v>14.07113198606357</v>
+        <v>14.05168589805019</v>
       </c>
       <c r="P6" t="n">
-        <v>316.8975882068293</v>
+        <v>316.8751333173747</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32044,28 +32135,28 @@
         <v>0.1291</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09184739485936742</v>
+        <v>0.08910683118097479</v>
       </c>
       <c r="J7" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K7" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003695778999979416</v>
+        <v>0.003496946323614414</v>
       </c>
       <c r="M7" t="n">
-        <v>8.847409883140704</v>
+        <v>8.836303151027126</v>
       </c>
       <c r="N7" t="n">
-        <v>123.2994552058077</v>
+        <v>123.0097069250243</v>
       </c>
       <c r="O7" t="n">
-        <v>11.10402878264496</v>
+        <v>11.09097411975271</v>
       </c>
       <c r="P7" t="n">
-        <v>331.6894690466788</v>
+        <v>331.7186110744701</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32122,28 +32213,28 @@
         <v>0.1133</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3716027909677195</v>
+        <v>0.3620895923229996</v>
       </c>
       <c r="J8" t="n">
+        <v>341</v>
+      </c>
+      <c r="K8" t="n">
         <v>340</v>
       </c>
-      <c r="K8" t="n">
-        <v>339</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.04555843560343775</v>
+        <v>0.04336098971108071</v>
       </c>
       <c r="M8" t="n">
-        <v>9.774217244767238</v>
+        <v>9.793956284151655</v>
       </c>
       <c r="N8" t="n">
-        <v>156.9679100860175</v>
+        <v>157.373729795181</v>
       </c>
       <c r="O8" t="n">
-        <v>12.5286834937282</v>
+        <v>12.54486866392713</v>
       </c>
       <c r="P8" t="n">
-        <v>325.2460725249258</v>
+        <v>325.3472793980146</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32200,28 +32291,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2481653098028561</v>
+        <v>0.2403081807963985</v>
       </c>
       <c r="J9" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K9" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01873540720236289</v>
+        <v>0.0176287831263392</v>
       </c>
       <c r="M9" t="n">
-        <v>10.42886946141109</v>
+        <v>10.44244186576949</v>
       </c>
       <c r="N9" t="n">
-        <v>171.3837918022237</v>
+        <v>171.4507427248971</v>
       </c>
       <c r="O9" t="n">
-        <v>13.09136325224473</v>
+        <v>13.09392006714937</v>
       </c>
       <c r="P9" t="n">
-        <v>321.4500942646804</v>
+        <v>321.5349942045474</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32278,28 +32369,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.040551732407809</v>
+        <v>-1.037183856601568</v>
       </c>
       <c r="J10" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K10" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05251822502170345</v>
+        <v>0.05247409170308082</v>
       </c>
       <c r="M10" t="n">
-        <v>21.55358564388974</v>
+        <v>21.49651434846967</v>
       </c>
       <c r="N10" t="n">
-        <v>1059.203894440834</v>
+        <v>1056.150003776554</v>
       </c>
       <c r="O10" t="n">
-        <v>32.54541280181945</v>
+        <v>32.4984615601501</v>
       </c>
       <c r="P10" t="n">
-        <v>332.3893995385479</v>
+        <v>332.3534874378592</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32356,28 +32447,28 @@
         <v>0.0462</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8557649293157844</v>
+        <v>-0.8459832673019787</v>
       </c>
       <c r="J11" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K11" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02971071982670315</v>
+        <v>0.02919759437519753</v>
       </c>
       <c r="M11" t="n">
-        <v>26.51203785483569</v>
+        <v>26.46652652397652</v>
       </c>
       <c r="N11" t="n">
-        <v>1281.37368218086</v>
+        <v>1278.406974572759</v>
       </c>
       <c r="O11" t="n">
-        <v>35.79628028414209</v>
+        <v>35.75481750160053</v>
       </c>
       <c r="P11" t="n">
-        <v>335.0960653115789</v>
+        <v>334.9908157923894</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32434,28 +32525,28 @@
         <v>0.0351</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.07134184663240149</v>
+        <v>-0.07173515149378096</v>
       </c>
       <c r="J12" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K12" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0004268249505259281</v>
+        <v>0.0004340199801005085</v>
       </c>
       <c r="M12" t="n">
-        <v>20.52827526856787</v>
+        <v>20.46949276112902</v>
       </c>
       <c r="N12" t="n">
-        <v>643.8426888409384</v>
+        <v>641.9336343910618</v>
       </c>
       <c r="O12" t="n">
-        <v>25.37405542756101</v>
+        <v>25.33640926396362</v>
       </c>
       <c r="P12" t="n">
-        <v>328.5579702236384</v>
+        <v>328.5621646557799</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32512,28 +32603,28 @@
         <v>0.098</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7288092250100728</v>
+        <v>0.7266238301533919</v>
       </c>
       <c r="J13" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K13" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04393870501139985</v>
+        <v>0.04392490696737106</v>
       </c>
       <c r="M13" t="n">
-        <v>20.34524903769911</v>
+        <v>20.29804096343784</v>
       </c>
       <c r="N13" t="n">
-        <v>618.6959689257098</v>
+        <v>616.8990725759834</v>
       </c>
       <c r="O13" t="n">
-        <v>24.87359983849764</v>
+        <v>24.83745302111276</v>
       </c>
       <c r="P13" t="n">
-        <v>315.4029031887647</v>
+        <v>315.4263597757356</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32590,28 +32681,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08826794358559638</v>
+        <v>0.08937465843046674</v>
       </c>
       <c r="J14" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K14" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0007449983297722618</v>
+        <v>0.0007681015358368404</v>
       </c>
       <c r="M14" t="n">
-        <v>19.81317433133425</v>
+        <v>19.75978292287529</v>
       </c>
       <c r="N14" t="n">
-        <v>563.2466999718819</v>
+        <v>561.5919443543835</v>
       </c>
       <c r="O14" t="n">
-        <v>23.73281904814263</v>
+        <v>23.69793122520157</v>
       </c>
       <c r="P14" t="n">
-        <v>327.2334840979381</v>
+        <v>327.2216386357255</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32668,28 +32759,28 @@
         <v>0.0863</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2704445230832961</v>
+        <v>-0.2680174641726057</v>
       </c>
       <c r="J15" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K15" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L15" t="n">
-        <v>0.006973567717858176</v>
+        <v>0.0068877674490051</v>
       </c>
       <c r="M15" t="n">
-        <v>19.64125590228717</v>
+        <v>19.59411146031141</v>
       </c>
       <c r="N15" t="n">
-        <v>561.3500611532467</v>
+        <v>559.7453142262251</v>
       </c>
       <c r="O15" t="n">
-        <v>23.6928272089518</v>
+        <v>23.65893730128691</v>
       </c>
       <c r="P15" t="n">
-        <v>341.734606488831</v>
+        <v>341.7086290342523</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32746,28 +32837,28 @@
         <v>0.0584</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1020587841185385</v>
+        <v>0.1032790988379799</v>
       </c>
       <c r="J16" t="n">
+        <v>341</v>
+      </c>
+      <c r="K16" t="n">
         <v>340</v>
       </c>
-      <c r="K16" t="n">
-        <v>339</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.003696006400333851</v>
+        <v>0.003805773522258193</v>
       </c>
       <c r="M16" t="n">
-        <v>9.919060803394467</v>
+        <v>9.895261512678278</v>
       </c>
       <c r="N16" t="n">
-        <v>152.3955487209251</v>
+        <v>151.9615108049134</v>
       </c>
       <c r="O16" t="n">
-        <v>12.34485920215071</v>
+        <v>12.32726696412929</v>
       </c>
       <c r="P16" t="n">
-        <v>349.8660194295571</v>
+        <v>349.8530602998082</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32824,28 +32915,28 @@
         <v>0.061</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1818892368597373</v>
+        <v>0.182177684909909</v>
       </c>
       <c r="J17" t="n">
+        <v>341</v>
+      </c>
+      <c r="K17" t="n">
         <v>340</v>
       </c>
-      <c r="K17" t="n">
-        <v>339</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.01530766292914576</v>
+        <v>0.0154412126736887</v>
       </c>
       <c r="M17" t="n">
-        <v>7.762531373955273</v>
+        <v>7.741171556661071</v>
       </c>
       <c r="N17" t="n">
-        <v>115.4723674119761</v>
+        <v>115.1335403311139</v>
       </c>
       <c r="O17" t="n">
-        <v>10.74580696885888</v>
+        <v>10.73002983831424</v>
       </c>
       <c r="P17" t="n">
-        <v>349.4037821974353</v>
+        <v>349.4007135213467</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32902,28 +32993,28 @@
         <v>0.0711</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2657406239553695</v>
+        <v>0.2648726939712475</v>
       </c>
       <c r="J18" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K18" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03779126356590223</v>
+        <v>0.03775677974532243</v>
       </c>
       <c r="M18" t="n">
-        <v>7.825966489482735</v>
+        <v>7.808091745615174</v>
       </c>
       <c r="N18" t="n">
-        <v>97.48443506788328</v>
+        <v>97.20576169102439</v>
       </c>
       <c r="O18" t="n">
-        <v>9.873420636632639</v>
+        <v>9.859298235220617</v>
       </c>
       <c r="P18" t="n">
-        <v>345.444974856434</v>
+        <v>345.4542040671682</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32980,28 +33071,28 @@
         <v>0.1025</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2882090095095238</v>
+        <v>0.2855320752112161</v>
       </c>
       <c r="J19" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K19" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03690792884893079</v>
+        <v>0.0364276093051995</v>
       </c>
       <c r="M19" t="n">
-        <v>8.724289764508583</v>
+        <v>8.712458221473801</v>
       </c>
       <c r="N19" t="n">
-        <v>117.8421029554334</v>
+        <v>117.5634125237033</v>
       </c>
       <c r="O19" t="n">
-        <v>10.85551025771858</v>
+        <v>10.84266630140868</v>
       </c>
       <c r="P19" t="n">
-        <v>340.2273978436512</v>
+        <v>340.255864290336</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33058,28 +33149,28 @@
         <v>0.0791</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5218290610950298</v>
+        <v>0.5194126398241683</v>
       </c>
       <c r="J20" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K20" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L20" t="n">
-        <v>0.09307242465678078</v>
+        <v>0.09273500737654983</v>
       </c>
       <c r="M20" t="n">
-        <v>9.537739161970906</v>
+        <v>9.52227489295087</v>
       </c>
       <c r="N20" t="n">
-        <v>143.8631608011951</v>
+        <v>143.4971209132649</v>
       </c>
       <c r="O20" t="n">
-        <v>11.99429701154658</v>
+        <v>11.97902837934967</v>
       </c>
       <c r="P20" t="n">
-        <v>333.8281815397461</v>
+        <v>333.8538767703974</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33136,28 +33227,28 @@
         <v>0.1044</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5434476311279818</v>
+        <v>0.5427373573764577</v>
       </c>
       <c r="J21" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K21" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L21" t="n">
-        <v>0.09269862806575435</v>
+        <v>0.09295180912823142</v>
       </c>
       <c r="M21" t="n">
-        <v>10.19310945317906</v>
+        <v>10.1671218488192</v>
       </c>
       <c r="N21" t="n">
-        <v>157.2422373466597</v>
+        <v>156.7832496680639</v>
       </c>
       <c r="O21" t="n">
-        <v>12.53962668290646</v>
+        <v>12.52131181897743</v>
       </c>
       <c r="P21" t="n">
-        <v>331.2404007692531</v>
+        <v>331.2479502707762</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33214,28 +33305,28 @@
         <v>0.1153</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5533648097958701</v>
+        <v>0.551926503474821</v>
       </c>
       <c r="J22" t="n">
+        <v>341</v>
+      </c>
+      <c r="K22" t="n">
         <v>340</v>
       </c>
-      <c r="K22" t="n">
-        <v>339</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.09177697653300043</v>
+        <v>0.09180480374531996</v>
       </c>
       <c r="M22" t="n">
-        <v>10.31356597035258</v>
+        <v>10.29174857456173</v>
       </c>
       <c r="N22" t="n">
-        <v>164.41984570824</v>
+        <v>163.9560875353023</v>
       </c>
       <c r="O22" t="n">
-        <v>12.82263021802626</v>
+        <v>12.80453386638117</v>
       </c>
       <c r="P22" t="n">
-        <v>328.9940558414563</v>
+        <v>329.0093573704933</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33292,28 +33383,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4546827248924841</v>
+        <v>0.457418525796498</v>
       </c>
       <c r="J23" t="n">
+        <v>341</v>
+      </c>
+      <c r="K23" t="n">
         <v>340</v>
       </c>
-      <c r="K23" t="n">
-        <v>339</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.06489968831015858</v>
+        <v>0.06595214085271683</v>
       </c>
       <c r="M23" t="n">
-        <v>10.00989876362197</v>
+        <v>9.994415723941366</v>
       </c>
       <c r="N23" t="n">
-        <v>161.6236458944387</v>
+        <v>161.2200253634043</v>
       </c>
       <c r="O23" t="n">
-        <v>12.71312887901474</v>
+        <v>12.69724479418288</v>
       </c>
       <c r="P23" t="n">
-        <v>328.9247256817967</v>
+        <v>328.8956206598972</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33370,28 +33461,28 @@
         <v>0.0646</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5835998315894793</v>
+        <v>0.5865153971008129</v>
       </c>
       <c r="J24" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K24" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L24" t="n">
-        <v>0.09846660500933957</v>
+        <v>0.09981994593653132</v>
       </c>
       <c r="M24" t="n">
-        <v>10.30328155291773</v>
+        <v>10.29024752687192</v>
       </c>
       <c r="N24" t="n">
-        <v>169.0692654579721</v>
+        <v>168.6547618156561</v>
       </c>
       <c r="O24" t="n">
-        <v>13.00266378316275</v>
+        <v>12.98671481998647</v>
       </c>
       <c r="P24" t="n">
-        <v>325.6654986223892</v>
+        <v>325.6344956970318</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33429,7 +33520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y341"/>
+  <dimension ref="A1:Y342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76507,6 +76598,133 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-38.4956388139673,174.63573947730177</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-38.495055532746605,174.63631798933588</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-38.494443051745336,174.63679411559428</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-38.4937742999696,174.63707291341342</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>-38.493037197025295,174.6372055968502</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>-38.492280296257434,174.6372493407755</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>-38.49154800367284,174.63738251504122</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>-38.49084449282569,174.63742562925393</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>-38.490141079363944,174.63745739431323</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>-38.48943993012943,174.63724190545148</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>-38.48873637348171,174.6372877708301</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>-38.48802995360712,174.63723495791473</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>-38.48732042945675,174.6371950909826</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>-38.48662023228381,174.63705071842492</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>-38.48592942713333,174.63681262118413</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>-38.48522771726267,174.63675465065748</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>-38.4845233660716,174.6367402247311</t>
+        </is>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>-38.483816207622375,174.63677208507565</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>-38.483114636361094,174.6367114846035</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>-38.482413680580265,174.63664059834124</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>-38.48170968246626,174.636619883822</t>
+        </is>
+      </c>
+      <c r="W342" t="inlineStr">
+        <is>
+          <t>-38.48101136818825,174.63650511219186</t>
+        </is>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>-38.480309949354705,174.63644154073708</t>
+        </is>
+      </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0260/nzd0260.xlsx
+++ b/data/nzd0260/nzd0260.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y342"/>
+  <dimension ref="A1:Y344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28025,7 +28025,7 @@
         <v>330.6</v>
       </c>
       <c r="N342" t="n">
-        <v>331.54</v>
+        <v>327.67</v>
       </c>
       <c r="O342" t="n">
         <v>339.03</v>
@@ -28060,6 +28060,168 @@
       <c r="Y342" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:06:14+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>334.12</v>
+      </c>
+      <c r="C343" t="n">
+        <v>309.14</v>
+      </c>
+      <c r="D343" t="n">
+        <v>294.85</v>
+      </c>
+      <c r="E343" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="F343" t="n">
+        <v>315.05</v>
+      </c>
+      <c r="G343" t="n">
+        <v>329.81</v>
+      </c>
+      <c r="H343" t="n">
+        <v>319.55</v>
+      </c>
+      <c r="I343" t="n">
+        <v>315.07</v>
+      </c>
+      <c r="J343" t="n">
+        <v>310.72</v>
+      </c>
+      <c r="K343" t="n">
+        <v>334.85</v>
+      </c>
+      <c r="L343" t="n">
+        <v>315.44</v>
+      </c>
+      <c r="M343" t="n">
+        <v>335.85</v>
+      </c>
+      <c r="N343" t="n">
+        <v>324.65</v>
+      </c>
+      <c r="O343" t="n">
+        <v>339.3</v>
+      </c>
+      <c r="P343" t="n">
+        <v>354.74</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>355.68</v>
+      </c>
+      <c r="R343" t="n">
+        <v>351.04</v>
+      </c>
+      <c r="S343" t="n">
+        <v>339.53</v>
+      </c>
+      <c r="T343" t="n">
+        <v>343.56</v>
+      </c>
+      <c r="U343" t="n">
+        <v>345.19</v>
+      </c>
+      <c r="V343" t="n">
+        <v>341.05</v>
+      </c>
+      <c r="W343" t="n">
+        <v>345.31</v>
+      </c>
+      <c r="X343" t="n">
+        <v>344.32</v>
+      </c>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>337.88</v>
+      </c>
+      <c r="C344" t="n">
+        <v>310.12</v>
+      </c>
+      <c r="D344" t="n">
+        <v>300.52</v>
+      </c>
+      <c r="E344" t="n">
+        <v>302.59</v>
+      </c>
+      <c r="F344" t="n">
+        <v>319.01</v>
+      </c>
+      <c r="G344" t="n">
+        <v>333.47</v>
+      </c>
+      <c r="H344" t="n">
+        <v>321.01</v>
+      </c>
+      <c r="I344" t="n">
+        <v>317.67</v>
+      </c>
+      <c r="J344" t="n">
+        <v>313.85</v>
+      </c>
+      <c r="K344" t="n">
+        <v>333.21</v>
+      </c>
+      <c r="L344" t="n">
+        <v>302.52</v>
+      </c>
+      <c r="M344" t="n">
+        <v>337.77</v>
+      </c>
+      <c r="N344" t="n">
+        <v>318.3</v>
+      </c>
+      <c r="O344" t="n">
+        <v>332.84</v>
+      </c>
+      <c r="P344" t="n">
+        <v>353.08</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>356.79</v>
+      </c>
+      <c r="R344" t="n">
+        <v>353.04</v>
+      </c>
+      <c r="S344" t="n">
+        <v>340.96</v>
+      </c>
+      <c r="T344" t="n">
+        <v>345.46</v>
+      </c>
+      <c r="U344" t="n">
+        <v>350.9</v>
+      </c>
+      <c r="V344" t="n">
+        <v>344.83</v>
+      </c>
+      <c r="W344" t="n">
+        <v>350.67</v>
+      </c>
+      <c r="X344" t="n">
+        <v>351.4</v>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28074,7 +28236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B350"/>
+  <dimension ref="A1:B352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31577,6 +31739,26 @@
       </c>
       <c r="B350" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>-0.8</v>
       </c>
     </row>
   </sheetData>
@@ -31745,28 +31927,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3905695832892048</v>
+        <v>-0.3700226568761028</v>
       </c>
       <c r="J2" t="n">
+        <v>343</v>
+      </c>
+      <c r="K2" t="n">
         <v>341</v>
       </c>
-      <c r="K2" t="n">
-        <v>339</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2043558067326735</v>
+        <v>0.1798442516764672</v>
       </c>
       <c r="M2" t="n">
-        <v>4.39054258206874</v>
+        <v>4.485433916810252</v>
       </c>
       <c r="N2" t="n">
-        <v>32.35457754493281</v>
+        <v>34.20251341023363</v>
       </c>
       <c r="O2" t="n">
-        <v>5.688108432944365</v>
+        <v>5.848291494978138</v>
       </c>
       <c r="P2" t="n">
-        <v>327.5685166185553</v>
+        <v>327.3484830448006</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31823,28 +32005,28 @@
         <v>0.1297</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4621705845832127</v>
+        <v>-0.4399131895254814</v>
       </c>
       <c r="J3" t="n">
+        <v>343</v>
+      </c>
+      <c r="K3" t="n">
         <v>341</v>
       </c>
-      <c r="K3" t="n">
-        <v>339</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1600636764157114</v>
+        <v>0.1438896299358806</v>
       </c>
       <c r="M3" t="n">
-        <v>6.077047700410667</v>
+        <v>6.171331058557159</v>
       </c>
       <c r="N3" t="n">
-        <v>61.06117523093619</v>
+        <v>63.07188982537312</v>
       </c>
       <c r="O3" t="n">
-        <v>7.814165037349555</v>
+        <v>7.94178127534202</v>
       </c>
       <c r="P3" t="n">
-        <v>301.526000834082</v>
+        <v>301.2876694726258</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31901,28 +32083,28 @@
         <v>0.1644</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1660672638412339</v>
+        <v>-0.1404968580267598</v>
       </c>
       <c r="J4" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K4" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01285292924570625</v>
+        <v>0.009089948870985132</v>
       </c>
       <c r="M4" t="n">
-        <v>8.395751691323193</v>
+        <v>8.478022256554974</v>
       </c>
       <c r="N4" t="n">
-        <v>114.5289608497657</v>
+        <v>116.9960572468155</v>
       </c>
       <c r="O4" t="n">
-        <v>10.70182044559549</v>
+        <v>10.81647157102608</v>
       </c>
       <c r="P4" t="n">
-        <v>278.9192945693093</v>
+        <v>278.6439238705443</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31979,28 +32161,28 @@
         <v>0.1682</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1667232352322437</v>
+        <v>-0.1532794993635021</v>
       </c>
       <c r="J5" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K5" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01342874108194447</v>
+        <v>0.01140996454905541</v>
       </c>
       <c r="M5" t="n">
-        <v>7.745130047972032</v>
+        <v>7.764842082950225</v>
       </c>
       <c r="N5" t="n">
-        <v>110.1357934525682</v>
+        <v>110.3951065574478</v>
       </c>
       <c r="O5" t="n">
-        <v>10.49456018385565</v>
+        <v>10.50690756395277</v>
       </c>
       <c r="P5" t="n">
-        <v>291.7482893050079</v>
+        <v>291.6032829926094</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32057,28 +32239,28 @@
         <v>0.1057</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2649450888638328</v>
+        <v>-0.2570766922007815</v>
       </c>
       <c r="J6" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K6" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01895163343695705</v>
+        <v>0.01803467768734446</v>
       </c>
       <c r="M6" t="n">
-        <v>11.6614515988144</v>
+        <v>11.63670275528896</v>
       </c>
       <c r="N6" t="n">
-        <v>197.4498765774626</v>
+        <v>196.5998492567205</v>
       </c>
       <c r="O6" t="n">
-        <v>14.05168589805019</v>
+        <v>14.02140682159677</v>
       </c>
       <c r="P6" t="n">
-        <v>316.8751333173747</v>
+        <v>316.7905131122079</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32135,28 +32317,28 @@
         <v>0.1291</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08910683118097479</v>
+        <v>0.08645078038136896</v>
       </c>
       <c r="J7" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K7" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003496946323614414</v>
+        <v>0.003328538232671985</v>
       </c>
       <c r="M7" t="n">
-        <v>8.836303151027126</v>
+        <v>8.799036347059545</v>
       </c>
       <c r="N7" t="n">
-        <v>123.0097069250243</v>
+        <v>122.3455763214935</v>
       </c>
       <c r="O7" t="n">
-        <v>11.09097411975271</v>
+        <v>11.06099345996974</v>
       </c>
       <c r="P7" t="n">
-        <v>331.7186110744701</v>
+        <v>331.7470110793301</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32213,28 +32395,28 @@
         <v>0.1133</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3620895923229996</v>
+        <v>0.3460702586545557</v>
       </c>
       <c r="J8" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K8" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04336098971108071</v>
+        <v>0.03989621069294769</v>
       </c>
       <c r="M8" t="n">
-        <v>9.793956284151655</v>
+        <v>9.816855924706152</v>
       </c>
       <c r="N8" t="n">
-        <v>157.373729795181</v>
+        <v>157.679786328408</v>
       </c>
       <c r="O8" t="n">
-        <v>12.54486866392713</v>
+        <v>12.55706121385127</v>
       </c>
       <c r="P8" t="n">
-        <v>325.3472793980146</v>
+        <v>325.5187795817769</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32291,28 +32473,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2403081807963985</v>
+        <v>0.2274639513253649</v>
       </c>
       <c r="J9" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K9" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0176287831263392</v>
+        <v>0.01593241169330728</v>
       </c>
       <c r="M9" t="n">
-        <v>10.44244186576949</v>
+        <v>10.45313001067256</v>
       </c>
       <c r="N9" t="n">
-        <v>171.4507427248971</v>
+        <v>171.214079946427</v>
       </c>
       <c r="O9" t="n">
-        <v>13.09392006714937</v>
+        <v>13.08487982162721</v>
       </c>
       <c r="P9" t="n">
-        <v>321.5349942045474</v>
+        <v>321.6746382779432</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32369,28 +32551,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.037183856601568</v>
+        <v>-1.029171972374915</v>
       </c>
       <c r="J10" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K10" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05247409170308082</v>
+        <v>0.05225963081490681</v>
       </c>
       <c r="M10" t="n">
-        <v>21.49651434846967</v>
+        <v>21.38573105912044</v>
       </c>
       <c r="N10" t="n">
-        <v>1056.150003776554</v>
+        <v>1050.200434890772</v>
       </c>
       <c r="O10" t="n">
-        <v>32.4984615601501</v>
+        <v>32.40679612196757</v>
       </c>
       <c r="P10" t="n">
-        <v>332.3534874378592</v>
+        <v>332.2674877879056</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32447,28 +32629,28 @@
         <v>0.0462</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8459832673019787</v>
+        <v>-0.822005828345458</v>
       </c>
       <c r="J11" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K11" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02919759437519753</v>
+        <v>0.02786656901286721</v>
       </c>
       <c r="M11" t="n">
-        <v>26.46652652397652</v>
+        <v>26.39132034766898</v>
       </c>
       <c r="N11" t="n">
-        <v>1278.406974572759</v>
+        <v>1273.423701949178</v>
       </c>
       <c r="O11" t="n">
-        <v>35.75481750160053</v>
+        <v>35.68506272867091</v>
       </c>
       <c r="P11" t="n">
-        <v>334.9908157923894</v>
+        <v>334.7311900464325</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32525,28 +32707,28 @@
         <v>0.0351</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.07173515149378096</v>
+        <v>-0.09142619395343393</v>
       </c>
       <c r="J12" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K12" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0004340199801005085</v>
+        <v>0.0007106966916849977</v>
       </c>
       <c r="M12" t="n">
-        <v>20.46949276112902</v>
+        <v>20.45608823425707</v>
       </c>
       <c r="N12" t="n">
-        <v>641.9336343910618</v>
+        <v>640.2071623520136</v>
       </c>
       <c r="O12" t="n">
-        <v>25.33640926396362</v>
+        <v>25.30231535555617</v>
       </c>
       <c r="P12" t="n">
-        <v>328.5621646557799</v>
+        <v>328.7735733657787</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32603,28 +32785,28 @@
         <v>0.098</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7266238301533919</v>
+        <v>0.7291689843231924</v>
       </c>
       <c r="J13" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K13" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04392490696737106</v>
+        <v>0.04470965571743524</v>
       </c>
       <c r="M13" t="n">
-        <v>20.29804096343784</v>
+        <v>20.18907586508727</v>
       </c>
       <c r="N13" t="n">
-        <v>616.8990725759834</v>
+        <v>613.2840136510614</v>
       </c>
       <c r="O13" t="n">
-        <v>24.83745302111276</v>
+        <v>24.76457174374436</v>
       </c>
       <c r="P13" t="n">
-        <v>315.4263597757356</v>
+        <v>315.3988578548038</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32681,28 +32863,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08937465843046674</v>
+        <v>0.0783059895291075</v>
       </c>
       <c r="J14" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K14" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0007681015358368404</v>
+        <v>0.0005960431084828244</v>
       </c>
       <c r="M14" t="n">
-        <v>19.75978292287529</v>
+        <v>19.6955090642547</v>
       </c>
       <c r="N14" t="n">
-        <v>561.5919443543835</v>
+        <v>558.722314830337</v>
       </c>
       <c r="O14" t="n">
-        <v>23.69793122520157</v>
+        <v>23.63730768997047</v>
       </c>
       <c r="P14" t="n">
-        <v>327.2216386357255</v>
+        <v>327.3407576831363</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32759,28 +32941,28 @@
         <v>0.0863</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2680174641726057</v>
+        <v>-0.2664631835294742</v>
       </c>
       <c r="J15" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K15" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0068877674490051</v>
+        <v>0.006885435586583832</v>
       </c>
       <c r="M15" t="n">
-        <v>19.59411146031141</v>
+        <v>19.49658621746521</v>
       </c>
       <c r="N15" t="n">
-        <v>559.7453142262251</v>
+        <v>556.5254316697185</v>
       </c>
       <c r="O15" t="n">
-        <v>23.65893730128691</v>
+        <v>23.5907912472159</v>
       </c>
       <c r="P15" t="n">
-        <v>341.7086290342523</v>
+        <v>341.6919278961464</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32837,28 +33019,28 @@
         <v>0.0584</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1032790988379799</v>
+        <v>0.1047556896507044</v>
       </c>
       <c r="J16" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K16" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L16" t="n">
-        <v>0.003805773522258193</v>
+        <v>0.003959625346510398</v>
       </c>
       <c r="M16" t="n">
-        <v>9.895261512678278</v>
+        <v>9.84377719826395</v>
       </c>
       <c r="N16" t="n">
-        <v>151.9615108049134</v>
+        <v>151.0872602762333</v>
       </c>
       <c r="O16" t="n">
-        <v>12.32726696412929</v>
+        <v>12.29175578492484</v>
       </c>
       <c r="P16" t="n">
-        <v>349.8530602998082</v>
+        <v>349.8372905236406</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32915,28 +33097,28 @@
         <v>0.061</v>
       </c>
       <c r="I17" t="n">
-        <v>0.182177684909909</v>
+        <v>0.1844254244437134</v>
       </c>
       <c r="J17" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K17" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0154412126736887</v>
+        <v>0.01599365567594924</v>
       </c>
       <c r="M17" t="n">
-        <v>7.741171556661071</v>
+        <v>7.707140169554815</v>
       </c>
       <c r="N17" t="n">
-        <v>115.1335403311139</v>
+        <v>114.4860766007121</v>
       </c>
       <c r="O17" t="n">
-        <v>10.73002983831424</v>
+        <v>10.69981666201398</v>
       </c>
       <c r="P17" t="n">
-        <v>349.4007135213467</v>
+        <v>349.3766414734022</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32993,28 +33175,28 @@
         <v>0.0711</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2648726939712475</v>
+        <v>0.2644567298431369</v>
       </c>
       <c r="J18" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K18" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03775677974532243</v>
+        <v>0.03805650501027258</v>
       </c>
       <c r="M18" t="n">
-        <v>7.808091745615174</v>
+        <v>7.768576386476358</v>
       </c>
       <c r="N18" t="n">
-        <v>97.20576169102439</v>
+        <v>96.645551603946</v>
       </c>
       <c r="O18" t="n">
-        <v>9.859298235220617</v>
+        <v>9.830846942351712</v>
       </c>
       <c r="P18" t="n">
-        <v>345.4542040671682</v>
+        <v>345.4586430153142</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33071,28 +33253,28 @@
         <v>0.1025</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2855320752112161</v>
+        <v>0.2772747266604631</v>
       </c>
       <c r="J19" t="n">
+        <v>343</v>
+      </c>
+      <c r="K19" t="n">
         <v>341</v>
       </c>
-      <c r="K19" t="n">
-        <v>339</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.0364276093051995</v>
+        <v>0.03470910612364175</v>
       </c>
       <c r="M19" t="n">
-        <v>8.712458221473801</v>
+        <v>8.703492176415031</v>
       </c>
       <c r="N19" t="n">
-        <v>117.5634125237033</v>
+        <v>117.2030829524755</v>
       </c>
       <c r="O19" t="n">
-        <v>10.84266630140868</v>
+        <v>10.82603726912463</v>
       </c>
       <c r="P19" t="n">
-        <v>340.255864290336</v>
+        <v>340.3442262072315</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33149,28 +33331,28 @@
         <v>0.0791</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5194126398241683</v>
+        <v>0.516116847693741</v>
       </c>
       <c r="J20" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K20" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L20" t="n">
-        <v>0.09273500737654983</v>
+        <v>0.09259211615458063</v>
       </c>
       <c r="M20" t="n">
-        <v>9.52227489295087</v>
+        <v>9.483500814293194</v>
       </c>
       <c r="N20" t="n">
-        <v>143.4971209132649</v>
+        <v>142.7172840595664</v>
       </c>
       <c r="O20" t="n">
-        <v>11.97902837934967</v>
+        <v>11.94643394739896</v>
       </c>
       <c r="P20" t="n">
-        <v>333.8538767703974</v>
+        <v>333.8891337224633</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33227,28 +33409,28 @@
         <v>0.1044</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5427373573764577</v>
+        <v>0.5455144980456572</v>
       </c>
       <c r="J21" t="n">
+        <v>343</v>
+      </c>
+      <c r="K21" t="n">
         <v>341</v>
       </c>
-      <c r="K21" t="n">
-        <v>339</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.09295180912823142</v>
+        <v>0.09474342551619563</v>
       </c>
       <c r="M21" t="n">
-        <v>10.1671218488192</v>
+        <v>10.12307608099407</v>
       </c>
       <c r="N21" t="n">
-        <v>156.7832496680639</v>
+        <v>155.9478004339594</v>
       </c>
       <c r="O21" t="n">
-        <v>12.52131181897743</v>
+        <v>12.48790616692644</v>
       </c>
       <c r="P21" t="n">
-        <v>331.2479502707762</v>
+        <v>331.2182073619756</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33305,28 +33487,28 @@
         <v>0.1153</v>
       </c>
       <c r="I22" t="n">
-        <v>0.551926503474821</v>
+        <v>0.5512852448577681</v>
       </c>
       <c r="J22" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K22" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L22" t="n">
-        <v>0.09180480374531996</v>
+        <v>0.09255375925644915</v>
       </c>
       <c r="M22" t="n">
-        <v>10.29174857456173</v>
+        <v>10.24291095978659</v>
       </c>
       <c r="N22" t="n">
-        <v>163.9560875353023</v>
+        <v>163.0198588617612</v>
       </c>
       <c r="O22" t="n">
-        <v>12.80453386638117</v>
+        <v>12.76792304416663</v>
       </c>
       <c r="P22" t="n">
-        <v>329.0093573704933</v>
+        <v>329.016199538551</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33383,28 +33565,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.457418525796498</v>
+        <v>0.4651790063089843</v>
       </c>
       <c r="J23" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K23" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L23" t="n">
-        <v>0.06595214085271683</v>
+        <v>0.06865190883942207</v>
       </c>
       <c r="M23" t="n">
-        <v>9.994415723941366</v>
+        <v>9.975152760360777</v>
       </c>
       <c r="N23" t="n">
-        <v>161.2200253634043</v>
+        <v>160.6055531808596</v>
       </c>
       <c r="O23" t="n">
-        <v>12.69724479418288</v>
+        <v>12.67302462638101</v>
       </c>
       <c r="P23" t="n">
-        <v>328.8956206598972</v>
+        <v>328.8125006331331</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33461,28 +33643,28 @@
         <v>0.0646</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5865153971008129</v>
+        <v>0.5939860446287494</v>
       </c>
       <c r="J24" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K24" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L24" t="n">
-        <v>0.09981994593653132</v>
+        <v>0.1029845907054682</v>
       </c>
       <c r="M24" t="n">
-        <v>10.29024752687192</v>
+        <v>10.27344354157089</v>
       </c>
       <c r="N24" t="n">
-        <v>168.6547618156561</v>
+        <v>168.0088276505913</v>
       </c>
       <c r="O24" t="n">
-        <v>12.98671481998647</v>
+        <v>12.96182192635709</v>
       </c>
       <c r="P24" t="n">
-        <v>325.6344956970318</v>
+        <v>325.5545077185225</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33520,7 +33702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y342"/>
+  <dimension ref="A1:Y344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76666,7 +76848,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t>-38.48732042945675,174.6371950909826</t>
+          <t>-38.48731832678616,174.6372393731407</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
@@ -76722,6 +76904,260 @@
       <c r="Y342" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:06:14+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-38.495629963851016,174.6357084390195</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>-38.49504877233453,174.63629427968922</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-38.49443472423414,174.63676490983227</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-38.49377199531901,174.63706483070794</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>-38.49303380019716,174.63719073596437</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-38.49227966444494,174.6372414715263</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-38.491548196363865,174.63736153744563</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-38.49084460970679,174.63741290526258</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>-38.49014102987278,174.63746278189672</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>-38.489440441762476,174.63718619607945</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>-38.48873526272016,174.63740870254156</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>-38.48803126654505,174.63717479828972</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>-38.48731668593084,174.63727392924116</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>-38.48662041898855,174.63704763249805</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>-38.48592942713333,174.63681262118413</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>-38.48522840181791,174.63674333580624</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>-38.484523511280095,174.6367378246345</t>
+        </is>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>-38.48381386352501,174.6368108291106</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>-38.483114954435536,174.6367062273512</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>-38.482414378953855,174.63662905535472</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>-38.481709806928606,174.63661782667606</t>
+        </is>
+      </c>
+      <c r="W343" t="inlineStr">
+        <is>
+          <t>-38.48101103629379,174.63651059786207</t>
+        </is>
+      </c>
+      <c r="X343" t="inlineStr">
+        <is>
+          <t>-38.48030862870159,174.6364633689227</t>
+        </is>
+      </c>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-38.4956184095199,174.6356679168287</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-38.49504576087666,174.63628371812072</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-38.49441730096705,174.63670380407078</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-38.49375297424768,174.6369981214641</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-38.4930238361569,174.63714714404017</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-38.49227631308295,174.63719973029342</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-38.49154835009279,174.63734480122162</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>-38.49084488347695,174.6373831013185</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>-38.49014135945812,174.637426902883</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>-38.489440269115605,174.637204995127</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>-38.488733902262034,174.63755680089173</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>-38.4880317466975,174.6371527970546</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>-38.48731323575489,174.63734658858525</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>-38.48661595188261,174.6371214661505</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>-38.485928279281524,174.6368315937432</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>-38.48522916934824,174.63673064945755</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>-38.48452489421567,174.636714966571</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>-38.48381485233461,174.63679448575698</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>-38.483116268218744,174.63668451261293</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>-38.4824183271635,174.63656379747528</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>-38.481712420629655,174.63657462660962</t>
+        </is>
+      </c>
+      <c r="W344" t="inlineStr">
+        <is>
+          <t>-38.48101474243389,174.63644934120808</t>
+        </is>
+      </c>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>-38.48031352408651,174.63638245606242</t>
+        </is>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0260/nzd0260.xlsx
+++ b/data/nzd0260/nzd0260.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y344"/>
+  <dimension ref="A1:Y346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28100,7 +28100,7 @@
         <v>334.85</v>
       </c>
       <c r="L343" t="n">
-        <v>315.44</v>
+        <v>334.88</v>
       </c>
       <c r="M343" t="n">
         <v>335.85</v>
@@ -28181,10 +28181,10 @@
         <v>333.21</v>
       </c>
       <c r="L344" t="n">
-        <v>302.52</v>
+        <v>334.88</v>
       </c>
       <c r="M344" t="n">
-        <v>337.77</v>
+        <v>330.12</v>
       </c>
       <c r="N344" t="n">
         <v>318.3</v>
@@ -28222,6 +28222,168 @@
       <c r="Y344" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>336.72</v>
+      </c>
+      <c r="C345" t="n">
+        <v>309.81</v>
+      </c>
+      <c r="D345" t="n">
+        <v>297.22</v>
+      </c>
+      <c r="E345" t="n">
+        <v>301.14</v>
+      </c>
+      <c r="F345" t="n">
+        <v>316.48</v>
+      </c>
+      <c r="G345" t="n">
+        <v>332.87</v>
+      </c>
+      <c r="H345" t="n">
+        <v>319.57</v>
+      </c>
+      <c r="I345" t="n">
+        <v>315.09</v>
+      </c>
+      <c r="J345" t="n">
+        <v>296.75</v>
+      </c>
+      <c r="K345" t="n">
+        <v>316.01</v>
+      </c>
+      <c r="L345" t="n">
+        <v>327.98</v>
+      </c>
+      <c r="M345" t="n">
+        <v>326</v>
+      </c>
+      <c r="N345" t="n">
+        <v>315.09</v>
+      </c>
+      <c r="O345" t="n">
+        <v>329.28</v>
+      </c>
+      <c r="P345" t="n">
+        <v>352.19</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>355.37</v>
+      </c>
+      <c r="R345" t="n">
+        <v>352.04</v>
+      </c>
+      <c r="S345" t="n">
+        <v>341.23</v>
+      </c>
+      <c r="T345" t="n">
+        <v>345.91</v>
+      </c>
+      <c r="U345" t="n">
+        <v>349.59</v>
+      </c>
+      <c r="V345" t="n">
+        <v>344.46</v>
+      </c>
+      <c r="W345" t="n">
+        <v>352.54</v>
+      </c>
+      <c r="X345" t="n">
+        <v>354.73</v>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>338.32</v>
+      </c>
+      <c r="C346" t="n">
+        <v>312</v>
+      </c>
+      <c r="D346" t="n">
+        <v>297.28</v>
+      </c>
+      <c r="E346" t="n">
+        <v>302.24</v>
+      </c>
+      <c r="F346" t="n">
+        <v>315.67</v>
+      </c>
+      <c r="G346" t="n">
+        <v>334.67</v>
+      </c>
+      <c r="H346" t="n">
+        <v>320.77</v>
+      </c>
+      <c r="I346" t="n">
+        <v>319.4</v>
+      </c>
+      <c r="J346" t="n">
+        <v>278.53</v>
+      </c>
+      <c r="K346" t="n">
+        <v>298.21</v>
+      </c>
+      <c r="L346" t="n">
+        <v>328.28</v>
+      </c>
+      <c r="M346" t="n">
+        <v>318.47</v>
+      </c>
+      <c r="N346" t="n">
+        <v>305.96</v>
+      </c>
+      <c r="O346" t="n">
+        <v>322.78</v>
+      </c>
+      <c r="P346" t="n">
+        <v>351.35</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>357.32</v>
+      </c>
+      <c r="R346" t="n">
+        <v>354.19</v>
+      </c>
+      <c r="S346" t="n">
+        <v>342.07</v>
+      </c>
+      <c r="T346" t="n">
+        <v>347.22</v>
+      </c>
+      <c r="U346" t="n">
+        <v>351.11</v>
+      </c>
+      <c r="V346" t="n">
+        <v>347.43</v>
+      </c>
+      <c r="W346" t="n">
+        <v>357.78</v>
+      </c>
+      <c r="X346" t="n">
+        <v>362.05</v>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28236,7 +28398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B352"/>
+  <dimension ref="A1:B354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31759,6 +31921,26 @@
       </c>
       <c r="B352" t="n">
         <v>-0.8</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>1.64</v>
       </c>
     </row>
   </sheetData>
@@ -31927,28 +32109,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3700226568761028</v>
+        <v>-0.3483673798582908</v>
       </c>
       <c r="J2" t="n">
+        <v>345</v>
+      </c>
+      <c r="K2" t="n">
         <v>343</v>
       </c>
-      <c r="K2" t="n">
-        <v>341</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1798442516764672</v>
+        <v>0.1555595248349441</v>
       </c>
       <c r="M2" t="n">
-        <v>4.485433916810252</v>
+        <v>4.58969694458518</v>
       </c>
       <c r="N2" t="n">
-        <v>34.20251341023363</v>
+        <v>36.28339242415971</v>
       </c>
       <c r="O2" t="n">
-        <v>5.848291494978138</v>
+        <v>6.023569740955915</v>
       </c>
       <c r="P2" t="n">
-        <v>327.3484830448006</v>
+        <v>327.1158590830753</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32005,28 +32187,28 @@
         <v>0.1297</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4399131895254814</v>
+        <v>-0.4168529599313838</v>
       </c>
       <c r="J3" t="n">
+        <v>345</v>
+      </c>
+      <c r="K3" t="n">
         <v>343</v>
       </c>
-      <c r="K3" t="n">
-        <v>341</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1438896299358806</v>
+        <v>0.1278378514147777</v>
       </c>
       <c r="M3" t="n">
-        <v>6.171331058557159</v>
+        <v>6.273422738341216</v>
       </c>
       <c r="N3" t="n">
-        <v>63.07188982537312</v>
+        <v>65.2926114696992</v>
       </c>
       <c r="O3" t="n">
-        <v>7.94178127534202</v>
+        <v>8.080384363982891</v>
       </c>
       <c r="P3" t="n">
-        <v>301.2876694726258</v>
+        <v>301.0399502440825</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32083,28 +32265,28 @@
         <v>0.1644</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1404968580267598</v>
+        <v>-0.1161064456548482</v>
       </c>
       <c r="J4" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K4" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009089948870985132</v>
+        <v>0.006145901108897123</v>
       </c>
       <c r="M4" t="n">
-        <v>8.478022256554974</v>
+        <v>8.556103634373123</v>
       </c>
       <c r="N4" t="n">
-        <v>116.9960572468155</v>
+        <v>119.1727106384304</v>
       </c>
       <c r="O4" t="n">
-        <v>10.81647157102608</v>
+        <v>10.91662542356521</v>
       </c>
       <c r="P4" t="n">
-        <v>278.6439238705443</v>
+        <v>278.3804646525401</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32161,28 +32343,28 @@
         <v>0.1682</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1532794993635021</v>
+        <v>-0.1377966472368171</v>
       </c>
       <c r="J5" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K5" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01140996454905541</v>
+        <v>0.009249847477374673</v>
       </c>
       <c r="M5" t="n">
-        <v>7.764842082950225</v>
+        <v>7.797112375151662</v>
       </c>
       <c r="N5" t="n">
-        <v>110.3951065574478</v>
+        <v>110.8989200047971</v>
       </c>
       <c r="O5" t="n">
-        <v>10.50690756395277</v>
+        <v>10.53085561598852</v>
       </c>
       <c r="P5" t="n">
-        <v>291.6032829926094</v>
+        <v>291.4357947007914</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32239,28 +32421,28 @@
         <v>0.1057</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2570766922007815</v>
+        <v>-0.2504551154564614</v>
       </c>
       <c r="J6" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K6" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01803467768734446</v>
+        <v>0.01730558989722619</v>
       </c>
       <c r="M6" t="n">
-        <v>11.63670275528896</v>
+        <v>11.60554605520268</v>
       </c>
       <c r="N6" t="n">
-        <v>196.5998492567205</v>
+        <v>195.6568260690297</v>
       </c>
       <c r="O6" t="n">
-        <v>14.02140682159677</v>
+        <v>13.98773841866618</v>
       </c>
       <c r="P6" t="n">
-        <v>316.7905131122079</v>
+        <v>316.719100782425</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32317,28 +32499,28 @@
         <v>0.1291</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08645078038136896</v>
+        <v>0.08617202009759942</v>
       </c>
       <c r="J7" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K7" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003328538232671985</v>
+        <v>0.003344540387863359</v>
       </c>
       <c r="M7" t="n">
-        <v>8.799036347059545</v>
+        <v>8.753228444745011</v>
       </c>
       <c r="N7" t="n">
-        <v>122.3455763214935</v>
+        <v>121.6413502300332</v>
       </c>
       <c r="O7" t="n">
-        <v>11.06099345996974</v>
+        <v>11.02911375542175</v>
       </c>
       <c r="P7" t="n">
-        <v>331.7470110793301</v>
+        <v>331.7499924813957</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32395,28 +32577,28 @@
         <v>0.1133</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3460702586545557</v>
+        <v>0.3303452017088331</v>
       </c>
       <c r="J8" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K8" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03989621069294769</v>
+        <v>0.03661152791936018</v>
       </c>
       <c r="M8" t="n">
-        <v>9.816855924706152</v>
+        <v>9.838242043024673</v>
       </c>
       <c r="N8" t="n">
-        <v>157.679786328408</v>
+        <v>157.9625975931206</v>
       </c>
       <c r="O8" t="n">
-        <v>12.55706121385127</v>
+        <v>12.56831721405537</v>
       </c>
       <c r="P8" t="n">
-        <v>325.5187795817769</v>
+        <v>325.6876630117776</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32473,28 +32655,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2274639513253649</v>
+        <v>0.2159270064682673</v>
       </c>
       <c r="J9" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K9" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01593241169330728</v>
+        <v>0.01448710323457592</v>
       </c>
       <c r="M9" t="n">
-        <v>10.45313001067256</v>
+        <v>10.45693399473966</v>
       </c>
       <c r="N9" t="n">
-        <v>171.214079946427</v>
+        <v>170.8642955678472</v>
       </c>
       <c r="O9" t="n">
-        <v>13.08487982162721</v>
+        <v>13.07150701211789</v>
       </c>
       <c r="P9" t="n">
-        <v>321.6746382779432</v>
+        <v>321.8004481576269</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32551,28 +32733,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.029171972374915</v>
+        <v>-1.048401929202415</v>
       </c>
       <c r="J10" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K10" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05225963081490681</v>
+        <v>0.0545974536946261</v>
       </c>
       <c r="M10" t="n">
-        <v>21.38573105912044</v>
+        <v>21.42294094610325</v>
       </c>
       <c r="N10" t="n">
-        <v>1050.200434890772</v>
+        <v>1046.265154445419</v>
       </c>
       <c r="O10" t="n">
-        <v>32.40679612196757</v>
+        <v>32.34602223528294</v>
       </c>
       <c r="P10" t="n">
-        <v>332.2674877879056</v>
+        <v>332.4746246233953</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32629,28 +32811,28 @@
         <v>0.0462</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.822005828345458</v>
+        <v>-0.8286515418776003</v>
       </c>
       <c r="J11" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K11" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02786656901286721</v>
+        <v>0.02860806495378099</v>
       </c>
       <c r="M11" t="n">
-        <v>26.39132034766898</v>
+        <v>26.29883416706988</v>
       </c>
       <c r="N11" t="n">
-        <v>1273.423701949178</v>
+        <v>1266.520368162308</v>
       </c>
       <c r="O11" t="n">
-        <v>35.68506272867091</v>
+        <v>35.58820546420272</v>
       </c>
       <c r="P11" t="n">
-        <v>334.7311900464325</v>
+        <v>334.8034931842126</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32707,28 +32889,28 @@
         <v>0.0351</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.09142619395343393</v>
+        <v>-0.06116234930767488</v>
       </c>
       <c r="J12" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K12" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0007106966916849977</v>
+        <v>0.0003226805914250397</v>
       </c>
       <c r="M12" t="n">
-        <v>20.45608823425707</v>
+        <v>20.28299248104275</v>
       </c>
       <c r="N12" t="n">
-        <v>640.2071623520136</v>
+        <v>634.8017294019278</v>
       </c>
       <c r="O12" t="n">
-        <v>25.30231535555617</v>
+        <v>25.19527196523046</v>
       </c>
       <c r="P12" t="n">
-        <v>328.7735733657787</v>
+        <v>328.4486449407919</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32785,28 +32967,28 @@
         <v>0.098</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7291689843231924</v>
+        <v>0.7112074723331431</v>
       </c>
       <c r="J13" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K13" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04470965571743524</v>
+        <v>0.04303066508233511</v>
       </c>
       <c r="M13" t="n">
-        <v>20.18907586508727</v>
+        <v>20.15971024782381</v>
       </c>
       <c r="N13" t="n">
-        <v>613.2840136510614</v>
+        <v>610.6658759209733</v>
       </c>
       <c r="O13" t="n">
-        <v>24.76457174374436</v>
+        <v>24.71165465769084</v>
       </c>
       <c r="P13" t="n">
-        <v>315.3988578548038</v>
+        <v>315.5934150362161</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32863,28 +33045,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0783059895291075</v>
+        <v>0.05764480313680738</v>
       </c>
       <c r="J14" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K14" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0005960431084828244</v>
+        <v>0.0003254922300923724</v>
       </c>
       <c r="M14" t="n">
-        <v>19.6955090642547</v>
+        <v>19.69867451531835</v>
       </c>
       <c r="N14" t="n">
-        <v>558.722314830337</v>
+        <v>557.6264921233233</v>
       </c>
       <c r="O14" t="n">
-        <v>23.63730768997047</v>
+        <v>23.61411637396841</v>
       </c>
       <c r="P14" t="n">
-        <v>327.3407576831363</v>
+        <v>327.564068339492</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32941,28 +33123,28 @@
         <v>0.0863</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2664631835294742</v>
+        <v>-0.2759146101736086</v>
       </c>
       <c r="J15" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K15" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L15" t="n">
-        <v>0.006885435586583832</v>
+        <v>0.007455589301508581</v>
       </c>
       <c r="M15" t="n">
-        <v>19.49658621746521</v>
+        <v>19.43956800457839</v>
       </c>
       <c r="N15" t="n">
-        <v>556.5254316697185</v>
+        <v>553.7611108190846</v>
       </c>
       <c r="O15" t="n">
-        <v>23.5907912472159</v>
+        <v>23.53212933032378</v>
       </c>
       <c r="P15" t="n">
-        <v>341.6919278961464</v>
+        <v>341.7940954787699</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33019,28 +33201,28 @@
         <v>0.0584</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1047556896507044</v>
+        <v>0.1038550865626709</v>
       </c>
       <c r="J16" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K16" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L16" t="n">
-        <v>0.003959625346510398</v>
+        <v>0.003936297320598525</v>
       </c>
       <c r="M16" t="n">
-        <v>9.84377719826395</v>
+        <v>9.792150596917118</v>
       </c>
       <c r="N16" t="n">
-        <v>151.0872602762333</v>
+        <v>150.2137824098042</v>
       </c>
       <c r="O16" t="n">
-        <v>12.29175578492484</v>
+        <v>12.25617323677355</v>
       </c>
       <c r="P16" t="n">
-        <v>349.8372905236406</v>
+        <v>349.8469506520208</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33097,28 +33279,28 @@
         <v>0.061</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1844254244437134</v>
+        <v>0.1867172817644913</v>
       </c>
       <c r="J17" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K17" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01599365567594924</v>
+        <v>0.01656574594344429</v>
       </c>
       <c r="M17" t="n">
-        <v>7.707140169554815</v>
+        <v>7.673702449797288</v>
       </c>
       <c r="N17" t="n">
-        <v>114.4860766007121</v>
+        <v>113.8513111354298</v>
       </c>
       <c r="O17" t="n">
-        <v>10.69981666201398</v>
+        <v>10.67011298606672</v>
       </c>
       <c r="P17" t="n">
-        <v>349.3766414734022</v>
+        <v>349.3520143870563</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33175,28 +33357,28 @@
         <v>0.0711</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2644567298431369</v>
+        <v>0.2651986035412284</v>
       </c>
       <c r="J18" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K18" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03805650501027258</v>
+        <v>0.03867703989898563</v>
       </c>
       <c r="M18" t="n">
-        <v>7.768576386476358</v>
+        <v>7.729328592557555</v>
       </c>
       <c r="N18" t="n">
-        <v>96.645551603946</v>
+        <v>96.09452204571765</v>
       </c>
       <c r="O18" t="n">
-        <v>9.830846942351712</v>
+        <v>9.80278134233941</v>
       </c>
       <c r="P18" t="n">
-        <v>345.4586430153142</v>
+        <v>345.4506660009717</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33253,28 +33435,28 @@
         <v>0.1025</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2772747266604631</v>
+        <v>0.2707518555666483</v>
       </c>
       <c r="J19" t="n">
+        <v>345</v>
+      </c>
+      <c r="K19" t="n">
         <v>343</v>
       </c>
-      <c r="K19" t="n">
-        <v>341</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.03470910612364175</v>
+        <v>0.03345453597707471</v>
       </c>
       <c r="M19" t="n">
-        <v>8.703492176415031</v>
+        <v>8.685782211827435</v>
       </c>
       <c r="N19" t="n">
-        <v>117.2030829524755</v>
+        <v>116.7274594127255</v>
       </c>
       <c r="O19" t="n">
-        <v>10.82603726912463</v>
+        <v>10.80404828815225</v>
       </c>
       <c r="P19" t="n">
-        <v>340.3442262072315</v>
+        <v>340.4142510942353</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33331,28 +33513,28 @@
         <v>0.0791</v>
       </c>
       <c r="I20" t="n">
-        <v>0.516116847693741</v>
+        <v>0.5151055466261603</v>
       </c>
       <c r="J20" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K20" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L20" t="n">
-        <v>0.09259211615458063</v>
+        <v>0.093210507565053</v>
       </c>
       <c r="M20" t="n">
-        <v>9.483500814293194</v>
+        <v>9.433604583724305</v>
       </c>
       <c r="N20" t="n">
-        <v>142.7172840595664</v>
+        <v>141.8973018731459</v>
       </c>
       <c r="O20" t="n">
-        <v>11.94643394739896</v>
+        <v>11.91206539073497</v>
       </c>
       <c r="P20" t="n">
-        <v>333.8891337224633</v>
+        <v>333.8999818903216</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33409,28 +33591,28 @@
         <v>0.1044</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5455144980456572</v>
+        <v>0.5506717724808236</v>
       </c>
       <c r="J21" t="n">
+        <v>345</v>
+      </c>
+      <c r="K21" t="n">
         <v>343</v>
       </c>
-      <c r="K21" t="n">
-        <v>341</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.09474342551619563</v>
+        <v>0.0972819029637485</v>
       </c>
       <c r="M21" t="n">
-        <v>10.12307608099407</v>
+        <v>10.08925794203553</v>
       </c>
       <c r="N21" t="n">
-        <v>155.9478004339594</v>
+        <v>155.1708960345931</v>
       </c>
       <c r="O21" t="n">
-        <v>12.48790616692644</v>
+        <v>12.45676105713653</v>
       </c>
       <c r="P21" t="n">
-        <v>331.2182073619756</v>
+        <v>331.1628549843865</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33487,28 +33669,28 @@
         <v>0.1153</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5512852448577681</v>
+        <v>0.5538876158162459</v>
       </c>
       <c r="J22" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K22" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L22" t="n">
-        <v>0.09255375925644915</v>
+        <v>0.09428447561272835</v>
       </c>
       <c r="M22" t="n">
-        <v>10.24291095978659</v>
+        <v>10.19552947885709</v>
       </c>
       <c r="N22" t="n">
-        <v>163.0198588617612</v>
+        <v>162.1173892411977</v>
       </c>
       <c r="O22" t="n">
-        <v>12.76792304416663</v>
+        <v>12.73253271117721</v>
       </c>
       <c r="P22" t="n">
-        <v>329.016199538551</v>
+        <v>328.9882312307376</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33565,28 +33747,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4651790063089843</v>
+        <v>0.48048328578427</v>
       </c>
       <c r="J23" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K23" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L23" t="n">
-        <v>0.06865190883942207</v>
+        <v>0.07317805197642357</v>
       </c>
       <c r="M23" t="n">
-        <v>9.975152760360777</v>
+        <v>9.993878658219247</v>
       </c>
       <c r="N23" t="n">
-        <v>160.6055531808596</v>
+        <v>160.8446812517093</v>
       </c>
       <c r="O23" t="n">
-        <v>12.67302462638101</v>
+        <v>12.68245564753567</v>
       </c>
       <c r="P23" t="n">
-        <v>328.8125006331331</v>
+        <v>328.648096807703</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33643,28 +33825,28 @@
         <v>0.0646</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5939860446287494</v>
+        <v>0.6126460907103413</v>
       </c>
       <c r="J24" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K24" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1029845907054682</v>
+        <v>0.1089232097415042</v>
       </c>
       <c r="M24" t="n">
-        <v>10.27344354157089</v>
+        <v>10.32077933033345</v>
       </c>
       <c r="N24" t="n">
-        <v>168.0088276505913</v>
+        <v>168.7928760465981</v>
       </c>
       <c r="O24" t="n">
-        <v>12.96182192635709</v>
+        <v>12.99203125175575</v>
       </c>
       <c r="P24" t="n">
-        <v>325.5545077185225</v>
+        <v>325.3541508937759</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33702,7 +33884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y344"/>
+  <dimension ref="A1:Y346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76965,7 +77147,7 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>-38.48873526272016,174.63740870254156</t>
+          <t>-38.48873730937249,174.63718586722996</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
@@ -77092,12 +77274,12 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>-38.488733902262034,174.63755680089173</t>
+          <t>-38.48873730937249,174.63718586722996</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>-38.4880317466975,174.6371527970546</t>
+          <t>-38.48802983356554,174.63724045822315</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -77158,6 +77340,260 @@
       <c r="Y344" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-38.4956219741555,174.63568041835433</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-38.49504671348079,174.63628705902497</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-38.49442744149683,174.63673936826714</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-38.49375742991408,174.63701374802062</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>-38.49303020207341,174.63717499443484</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>-38.492276862487564,174.63720657311825</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-38.49154819846975,174.63736130818228</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>-38.49084461181275,174.63741267600147</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>-38.490139558714084,174.63762291921117</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>-38.489438458247164,174.63740215585753</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>-38.48873658298576,174.63726496001348</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>-38.48802880319804,174.63728766920252</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>-38.487311491633086,174.63738331873859</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>-38.48661349011402,174.63716215466022</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>-38.48592766386573,174.6368417657776</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>-38.48522818746234,174.6367468788405</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>-38.484524202748446,174.63672639560286</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>-38.483815039032656,174.63679139994892</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>-38.483116579377345,174.6366793696485</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>-38.48241742136029,174.6365787690736</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>-38.481712164791894,174.6365788551877</t>
+        </is>
+      </c>
+      <c r="W345" t="inlineStr">
+        <is>
+          <t>-38.48101603542676,174.6364279699483</t>
+        </is>
+      </c>
+      <c r="X345" t="inlineStr">
+        <is>
+          <t>-38.48031582655761,174.63634439958554</t>
+        </is>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-38.49561705741638,174.63566317487104</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-38.495039983791486,174.636263457155</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-38.49442725712366,174.6367387216453</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-38.49375404975355,174.63700189339139</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>-38.493032240171736,174.63718391096538</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-38.492275214272475,174.637186044644</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>-38.49154832482246,174.63734755238173</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>-38.490845065635206,174.6373632702324</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>-38.49013763966567,174.63783177401194</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>-38.489436583859536,174.637606194265</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>-38.488736614568914,174.6372615211969</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>-38.48802691997726,174.6373739552834</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>-38.48730653087496,174.63748778797904</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>-38.48660899527548,174.63723644547008</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>-38.48592708302305,174.63685136634922</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>-38.4852295358262,174.63672459201172</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>-38.48452568940161,174.636701823184</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>-38.483815619870555,174.63678179965697</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>-38.48311748519331,174.6366643979072</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>-38.48241847236843,174.63656139744802</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>-38.481714218404235,174.63654491227607</t>
+        </is>
+      </c>
+      <c r="W346" t="inlineStr">
+        <is>
+          <t>-38.48101965855184,174.63636808470227</t>
+        </is>
+      </c>
+      <c r="X346" t="inlineStr">
+        <is>
+          <t>-38.480320887802165,174.63626074389651</t>
+        </is>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0260/nzd0260.xlsx
+++ b/data/nzd0260/nzd0260.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y346"/>
+  <dimension ref="A1:Y347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28256,7 +28256,7 @@
         <v>315.09</v>
       </c>
       <c r="J345" t="n">
-        <v>296.75</v>
+        <v>313.85</v>
       </c>
       <c r="K345" t="n">
         <v>316.01</v>
@@ -28337,7 +28337,7 @@
         <v>319.4</v>
       </c>
       <c r="J346" t="n">
-        <v>278.53</v>
+        <v>319.86</v>
       </c>
       <c r="K346" t="n">
         <v>298.21</v>
@@ -28384,6 +28384,87 @@
       <c r="Y346" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>336.89</v>
+      </c>
+      <c r="C347" t="n">
+        <v>309.62</v>
+      </c>
+      <c r="D347" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="E347" t="n">
+        <v>301.57</v>
+      </c>
+      <c r="F347" t="n">
+        <v>311.62</v>
+      </c>
+      <c r="G347" t="n">
+        <v>331.57</v>
+      </c>
+      <c r="H347" t="n">
+        <v>313.74</v>
+      </c>
+      <c r="I347" t="n">
+        <v>312.84</v>
+      </c>
+      <c r="J347" t="n">
+        <v>305.77</v>
+      </c>
+      <c r="K347" t="n">
+        <v>288.91</v>
+      </c>
+      <c r="L347" t="n">
+        <v>317.77</v>
+      </c>
+      <c r="M347" t="n">
+        <v>311.24</v>
+      </c>
+      <c r="N347" t="n">
+        <v>299.1</v>
+      </c>
+      <c r="O347" t="n">
+        <v>316.03</v>
+      </c>
+      <c r="P347" t="n">
+        <v>345.6</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>354.32</v>
+      </c>
+      <c r="R347" t="n">
+        <v>353.21</v>
+      </c>
+      <c r="S347" t="n">
+        <v>342.97</v>
+      </c>
+      <c r="T347" t="n">
+        <v>346.75</v>
+      </c>
+      <c r="U347" t="n">
+        <v>348.43</v>
+      </c>
+      <c r="V347" t="n">
+        <v>344.68</v>
+      </c>
+      <c r="W347" t="n">
+        <v>357.14</v>
+      </c>
+      <c r="X347" t="n">
+        <v>363.4</v>
+      </c>
+      <c r="Y347" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28398,7 +28479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B354"/>
+  <dimension ref="A1:B355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31941,6 +32022,16 @@
       </c>
       <c r="B354" t="n">
         <v>1.64</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0.21</v>
       </c>
     </row>
   </sheetData>
@@ -32109,28 +32200,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3483673798582908</v>
+        <v>-0.3380009138883273</v>
       </c>
       <c r="J2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K2" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1555595248349441</v>
+        <v>0.1449537762692654</v>
       </c>
       <c r="M2" t="n">
-        <v>4.58969694458518</v>
+        <v>4.638996379619591</v>
       </c>
       <c r="N2" t="n">
-        <v>36.28339242415971</v>
+        <v>37.2187223951915</v>
       </c>
       <c r="O2" t="n">
-        <v>6.023569740955915</v>
+        <v>6.100714908532565</v>
       </c>
       <c r="P2" t="n">
-        <v>327.1158590830753</v>
+        <v>327.0038024941933</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32187,28 +32278,28 @@
         <v>0.1297</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4168529599313838</v>
+        <v>-0.4061475069697784</v>
       </c>
       <c r="J3" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K3" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1278378514147777</v>
+        <v>0.1209497608996013</v>
       </c>
       <c r="M3" t="n">
-        <v>6.273422738341216</v>
+        <v>6.318747008350343</v>
       </c>
       <c r="N3" t="n">
-        <v>65.2926114696992</v>
+        <v>66.21279461866338</v>
       </c>
       <c r="O3" t="n">
-        <v>8.080384363982891</v>
+        <v>8.137124468672171</v>
       </c>
       <c r="P3" t="n">
-        <v>301.0399502440825</v>
+        <v>300.9242293663224</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32265,28 +32356,28 @@
         <v>0.1644</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1161064456548482</v>
+        <v>-0.1055695234315465</v>
       </c>
       <c r="J4" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K4" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006145901108897123</v>
+        <v>0.005070136522824398</v>
       </c>
       <c r="M4" t="n">
-        <v>8.556103634373123</v>
+        <v>8.586855871116562</v>
       </c>
       <c r="N4" t="n">
-        <v>119.1727106384304</v>
+        <v>119.8902656143511</v>
       </c>
       <c r="O4" t="n">
-        <v>10.91662542356521</v>
+        <v>10.94944133800218</v>
       </c>
       <c r="P4" t="n">
-        <v>278.3804646525401</v>
+        <v>278.2659320888848</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32343,28 +32434,28 @@
         <v>0.1682</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1377966472368171</v>
+        <v>-0.1302125797326745</v>
       </c>
       <c r="J5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K5" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009249847477374673</v>
+        <v>0.008274043074382953</v>
       </c>
       <c r="M5" t="n">
-        <v>7.797112375151662</v>
+        <v>7.813286258641899</v>
       </c>
       <c r="N5" t="n">
-        <v>110.8989200047971</v>
+        <v>111.1249434420667</v>
       </c>
       <c r="O5" t="n">
-        <v>10.53085561598852</v>
+        <v>10.54158163854299</v>
       </c>
       <c r="P5" t="n">
-        <v>291.4357947007914</v>
+        <v>291.3532421357866</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32421,28 +32512,28 @@
         <v>0.1057</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2504551154564614</v>
+        <v>-0.2496094318312437</v>
       </c>
       <c r="J6" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K6" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01730558989722619</v>
+        <v>0.0172866012187598</v>
       </c>
       <c r="M6" t="n">
-        <v>11.60554605520268</v>
+        <v>11.57621501340498</v>
       </c>
       <c r="N6" t="n">
-        <v>195.6568260690297</v>
+        <v>195.0899644958681</v>
       </c>
       <c r="O6" t="n">
-        <v>13.98773841866618</v>
+        <v>13.96746091800038</v>
       </c>
       <c r="P6" t="n">
-        <v>316.719100782425</v>
+        <v>316.709921696128</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32499,28 +32590,28 @@
         <v>0.1291</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08617202009759942</v>
+        <v>0.0848296335137633</v>
       </c>
       <c r="J7" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K7" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003344540387863359</v>
+        <v>0.003259496942368378</v>
       </c>
       <c r="M7" t="n">
-        <v>8.753228444745011</v>
+        <v>8.735054763663756</v>
       </c>
       <c r="N7" t="n">
-        <v>121.6413502300332</v>
+        <v>121.3071555767591</v>
       </c>
       <c r="O7" t="n">
-        <v>11.02911375542175</v>
+        <v>11.0139527680465</v>
       </c>
       <c r="P7" t="n">
-        <v>331.7499924813957</v>
+        <v>331.7644930230948</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32577,28 +32668,28 @@
         <v>0.1133</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3303452017088331</v>
+        <v>0.3190529906710373</v>
       </c>
       <c r="J8" t="n">
+        <v>346</v>
+      </c>
+      <c r="K8" t="n">
         <v>345</v>
       </c>
-      <c r="K8" t="n">
-        <v>344</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.03661152791936018</v>
+        <v>0.03416635158490966</v>
       </c>
       <c r="M8" t="n">
-        <v>9.838242043024673</v>
+        <v>9.865590031486841</v>
       </c>
       <c r="N8" t="n">
-        <v>157.9625975931206</v>
+        <v>158.7364123290663</v>
       </c>
       <c r="O8" t="n">
-        <v>12.56831721405537</v>
+        <v>12.59906394654247</v>
       </c>
       <c r="P8" t="n">
-        <v>325.6876630117776</v>
+        <v>325.8097067593864</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32655,28 +32746,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2159270064682673</v>
+        <v>0.2077676164997153</v>
       </c>
       <c r="J9" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K9" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01448710323457592</v>
+        <v>0.0134548174177278</v>
       </c>
       <c r="M9" t="n">
-        <v>10.45693399473966</v>
+        <v>10.47236326852221</v>
       </c>
       <c r="N9" t="n">
-        <v>170.8642955678472</v>
+        <v>170.9899792668685</v>
       </c>
       <c r="O9" t="n">
-        <v>13.07150701211789</v>
+        <v>13.07631367270105</v>
       </c>
       <c r="P9" t="n">
-        <v>321.8004481576269</v>
+        <v>321.8899973061266</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32733,28 +32824,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.048401929202415</v>
+        <v>-1.015969749239461</v>
       </c>
       <c r="J10" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K10" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0545974536946261</v>
+        <v>0.05178936214124086</v>
       </c>
       <c r="M10" t="n">
-        <v>21.42294094610325</v>
+        <v>21.2241322239454</v>
       </c>
       <c r="N10" t="n">
-        <v>1046.265154445419</v>
+        <v>1041.783808102817</v>
       </c>
       <c r="O10" t="n">
-        <v>32.34602223528294</v>
+        <v>32.27667591470375</v>
       </c>
       <c r="P10" t="n">
-        <v>332.4746246233953</v>
+        <v>332.125298148104</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32811,28 +32902,28 @@
         <v>0.0462</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8286515418776003</v>
+        <v>-0.8420331512791492</v>
       </c>
       <c r="J11" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K11" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02860806495378099</v>
+        <v>0.02963944926224493</v>
       </c>
       <c r="M11" t="n">
-        <v>26.29883416706988</v>
+        <v>26.31556543207968</v>
       </c>
       <c r="N11" t="n">
-        <v>1266.520368162308</v>
+        <v>1264.446709161219</v>
       </c>
       <c r="O11" t="n">
-        <v>35.58820546420272</v>
+        <v>35.55905945270796</v>
       </c>
       <c r="P11" t="n">
-        <v>334.8034931842126</v>
+        <v>334.9497640440117</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32889,28 +32980,28 @@
         <v>0.0351</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.06116234930767488</v>
+        <v>-0.06616242615271747</v>
       </c>
       <c r="J12" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K12" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0003226805914250397</v>
+        <v>0.0003796139556014877</v>
       </c>
       <c r="M12" t="n">
-        <v>20.28299248104275</v>
+        <v>20.2513617656634</v>
       </c>
       <c r="N12" t="n">
-        <v>634.8017294019278</v>
+        <v>633.18322172534</v>
       </c>
       <c r="O12" t="n">
-        <v>25.19527196523046</v>
+        <v>25.16313219226375</v>
       </c>
       <c r="P12" t="n">
-        <v>328.4486449407919</v>
+        <v>328.5028119480291</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32967,28 +33058,28 @@
         <v>0.098</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7112074723331431</v>
+        <v>0.6982975226559193</v>
       </c>
       <c r="J13" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K13" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04303066508233511</v>
+        <v>0.0416752058991533</v>
       </c>
       <c r="M13" t="n">
-        <v>20.15971024782381</v>
+        <v>20.17759251018267</v>
       </c>
       <c r="N13" t="n">
-        <v>610.6658759209733</v>
+        <v>610.4397290293646</v>
       </c>
       <c r="O13" t="n">
-        <v>24.71165465769084</v>
+        <v>24.7070785207269</v>
       </c>
       <c r="P13" t="n">
-        <v>315.5934150362161</v>
+        <v>315.7341582247729</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33045,28 +33136,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05764480313680738</v>
+        <v>0.04117816761434455</v>
       </c>
       <c r="J14" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K14" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0003254922300923724</v>
+        <v>0.0001662926617617133</v>
       </c>
       <c r="M14" t="n">
-        <v>19.69867451531835</v>
+        <v>19.73529613653014</v>
       </c>
       <c r="N14" t="n">
-        <v>557.6264921233233</v>
+        <v>558.6000740888064</v>
       </c>
       <c r="O14" t="n">
-        <v>23.61411637396841</v>
+        <v>23.63472178995992</v>
       </c>
       <c r="P14" t="n">
-        <v>327.564068339492</v>
+        <v>327.7431157362971</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33123,28 +33214,28 @@
         <v>0.0863</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2759146101736086</v>
+        <v>-0.2860493062086067</v>
       </c>
       <c r="J15" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K15" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L15" t="n">
-        <v>0.007455589301508581</v>
+        <v>0.00804007276319052</v>
       </c>
       <c r="M15" t="n">
-        <v>19.43956800457839</v>
+        <v>19.44305793611063</v>
       </c>
       <c r="N15" t="n">
-        <v>553.7611108190846</v>
+        <v>553.1312714722401</v>
       </c>
       <c r="O15" t="n">
-        <v>23.53212933032378</v>
+        <v>23.51874298240108</v>
       </c>
       <c r="P15" t="n">
-        <v>341.7940954787699</v>
+        <v>341.9042935177076</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33201,28 +33292,28 @@
         <v>0.0584</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1038550865626709</v>
+        <v>0.1000273036029642</v>
       </c>
       <c r="J16" t="n">
+        <v>346</v>
+      </c>
+      <c r="K16" t="n">
         <v>345</v>
       </c>
-      <c r="K16" t="n">
-        <v>344</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.003936297320598525</v>
+        <v>0.003670003349405815</v>
       </c>
       <c r="M16" t="n">
-        <v>9.792150596917118</v>
+        <v>9.787316969024587</v>
       </c>
       <c r="N16" t="n">
-        <v>150.2137824098042</v>
+        <v>149.9190954196091</v>
       </c>
       <c r="O16" t="n">
-        <v>12.25617323677355</v>
+        <v>12.24414535276387</v>
       </c>
       <c r="P16" t="n">
-        <v>349.8469506520208</v>
+        <v>349.8882432987892</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33279,28 +33370,28 @@
         <v>0.061</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1867172817644913</v>
+        <v>0.1867263761425021</v>
       </c>
       <c r="J17" t="n">
+        <v>346</v>
+      </c>
+      <c r="K17" t="n">
         <v>345</v>
       </c>
-      <c r="K17" t="n">
-        <v>344</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.01656574594344429</v>
+        <v>0.01666037171175894</v>
       </c>
       <c r="M17" t="n">
-        <v>7.673702449797288</v>
+        <v>7.651504390941679</v>
       </c>
       <c r="N17" t="n">
-        <v>113.8513111354298</v>
+        <v>113.5213081339235</v>
       </c>
       <c r="O17" t="n">
-        <v>10.67011298606672</v>
+        <v>10.65463786967551</v>
       </c>
       <c r="P17" t="n">
-        <v>349.3520143870563</v>
+        <v>349.3519160970074</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33357,28 +33448,28 @@
         <v>0.0711</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2651986035412284</v>
+        <v>0.2655971259154432</v>
       </c>
       <c r="J18" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K18" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03867703989898563</v>
+        <v>0.03900143830321556</v>
       </c>
       <c r="M18" t="n">
-        <v>7.729328592557555</v>
+        <v>7.708870917073014</v>
       </c>
       <c r="N18" t="n">
-        <v>96.09452204571765</v>
+        <v>95.81832311947691</v>
       </c>
       <c r="O18" t="n">
-        <v>9.80278134233941</v>
+        <v>9.788683421148981</v>
       </c>
       <c r="P18" t="n">
-        <v>345.4506660009717</v>
+        <v>345.4463611379949</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33435,28 +33526,28 @@
         <v>0.1025</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2707518555666483</v>
+        <v>0.2682332024457916</v>
       </c>
       <c r="J19" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K19" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03345453597707471</v>
+        <v>0.03301967734248201</v>
       </c>
       <c r="M19" t="n">
-        <v>8.685782211827435</v>
+        <v>8.673320106823478</v>
       </c>
       <c r="N19" t="n">
-        <v>116.7274594127255</v>
+        <v>116.4496139228876</v>
       </c>
       <c r="O19" t="n">
-        <v>10.80404828815225</v>
+        <v>10.79118223008432</v>
       </c>
       <c r="P19" t="n">
-        <v>340.4142510942353</v>
+        <v>340.4414624288825</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33513,28 +33604,28 @@
         <v>0.0791</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5151055466261603</v>
+        <v>0.5146693228932174</v>
       </c>
       <c r="J20" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K20" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L20" t="n">
-        <v>0.093210507565053</v>
+        <v>0.09354874497006471</v>
       </c>
       <c r="M20" t="n">
-        <v>9.433604583724305</v>
+        <v>9.408492991457413</v>
       </c>
       <c r="N20" t="n">
-        <v>141.8973018731459</v>
+        <v>141.4890283279201</v>
       </c>
       <c r="O20" t="n">
-        <v>11.91206539073497</v>
+        <v>11.89491607065473</v>
       </c>
       <c r="P20" t="n">
-        <v>333.8999818903216</v>
+        <v>333.9046940056733</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33591,28 +33682,28 @@
         <v>0.1044</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5506717724808236</v>
+        <v>0.5521300125668938</v>
       </c>
       <c r="J21" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K21" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0972819029637485</v>
+        <v>0.09823836566301936</v>
       </c>
       <c r="M21" t="n">
-        <v>10.08925794203553</v>
+        <v>10.06694230815042</v>
       </c>
       <c r="N21" t="n">
-        <v>155.1708960345931</v>
+        <v>154.7404325351309</v>
       </c>
       <c r="O21" t="n">
-        <v>12.45676105713653</v>
+        <v>12.43947074980005</v>
       </c>
       <c r="P21" t="n">
-        <v>331.1628549843865</v>
+        <v>331.1471075854585</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33669,28 +33760,28 @@
         <v>0.1153</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5538876158162459</v>
+        <v>0.5544413976137492</v>
       </c>
       <c r="J22" t="n">
+        <v>346</v>
+      </c>
+      <c r="K22" t="n">
         <v>345</v>
       </c>
-      <c r="K22" t="n">
-        <v>344</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.09428447561272835</v>
+        <v>0.09494192525308154</v>
       </c>
       <c r="M22" t="n">
-        <v>10.19552947885709</v>
+        <v>10.16852786571663</v>
       </c>
       <c r="N22" t="n">
-        <v>162.1173892411977</v>
+        <v>161.6504459784663</v>
       </c>
       <c r="O22" t="n">
-        <v>12.73253271117721</v>
+        <v>12.71418286711601</v>
       </c>
       <c r="P22" t="n">
-        <v>328.9882312307376</v>
+        <v>328.9822460781666</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33747,28 +33838,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.48048328578427</v>
+        <v>0.4890768807185916</v>
       </c>
       <c r="J23" t="n">
+        <v>346</v>
+      </c>
+      <c r="K23" t="n">
         <v>345</v>
       </c>
-      <c r="K23" t="n">
-        <v>344</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.07317805197642357</v>
+        <v>0.07570727014055589</v>
       </c>
       <c r="M23" t="n">
-        <v>9.993878658219247</v>
+        <v>10.00817393423064</v>
       </c>
       <c r="N23" t="n">
-        <v>160.8446812517093</v>
+        <v>161.0917919058778</v>
       </c>
       <c r="O23" t="n">
-        <v>12.68245564753567</v>
+        <v>12.69219413284708</v>
       </c>
       <c r="P23" t="n">
-        <v>328.648096807703</v>
+        <v>328.5552191128295</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33825,28 +33916,28 @@
         <v>0.0646</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6126460907103413</v>
+        <v>0.6245362048303668</v>
       </c>
       <c r="J24" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K24" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1089232097415042</v>
+        <v>0.1124750365858672</v>
       </c>
       <c r="M24" t="n">
-        <v>10.32077933033345</v>
+        <v>10.35872995900633</v>
       </c>
       <c r="N24" t="n">
-        <v>168.7928760465981</v>
+        <v>169.6677823412375</v>
       </c>
       <c r="O24" t="n">
-        <v>12.99203125175575</v>
+        <v>13.02565861449</v>
       </c>
       <c r="P24" t="n">
-        <v>325.3541508937759</v>
+        <v>325.2257131563309</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33884,7 +33975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y346"/>
+  <dimension ref="A1:Y347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77391,7 +77482,7 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>-38.490139558714084,174.63762291921117</t>
+          <t>-38.49014135945812,174.637426902883</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -77518,7 +77609,7 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>-38.49013763966567,174.63783177401194</t>
+          <t>-38.49014199227332,174.63735801058942</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -77594,6 +77685,133 @@
       <c r="Y346" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-38.495621451752086,174.63567858623412</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-38.495047297334864,174.636289106676</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-38.49443579974337,174.6367686817938</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>-38.49375610857875,174.63700911393815</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>-38.49304243065302,174.63722849362514</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>-38.49227805286289,174.63722139923902</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>-38.491547584583245,174.63742813844505</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>-38.490844374890195,174.63743846787574</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>-38.49014050862112,174.63751952346647</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>-38.489435604403305,174.6377127985922</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>-38.48873550804601,174.63738199440127</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>-38.48802511172542,174.63745680366543</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>-38.4873028034534,174.6375662829279</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>-38.486604327508864,174.63731359360725</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>-38.48592310699559,174.63691708454274</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>-38.48522746141852,174.6367588794402</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>-38.48452501176498,174.63671302363554</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>-38.483816242195985,174.6367715136297</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>-38.483117160206135,174.63666976944802</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>-38.48241661927342,174.63659202636637</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>-38.48171231691166,174.63657634089805</t>
+        </is>
+      </c>
+      <c r="W347" t="inlineStr">
+        <is>
+          <t>-38.4810192160344,174.63637539893116</t>
+        </is>
+      </c>
+      <c r="X347" t="inlineStr">
+        <is>
+          <t>-38.4803218212219,174.6362453155917</t>
+        </is>
+      </c>
+      <c r="Y347" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
